--- a/filer/63049611_hartmann.xlsx
+++ b/filer/63049611_hartmann.xlsx
@@ -5335,7 +5335,9 @@
       <c r="E21" s="16" t="n">
         <v>54700</v>
       </c>
-      <c r="F21" s="16" t="n"/>
+      <c r="F21" s="16" t="n">
+        <v>57200</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
@@ -7171,7 +7173,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -7334,12 +7336,12 @@
       </c>
       <c r="B6" s="37" t="inlineStr">
         <is>
-          <t>fsa:NoncurrentDeferredTaxAssets</t>
+          <t>fsa:OtherProvisionsLiabilitiesShortterm</t>
         </is>
       </c>
       <c r="C6" s="37" t="inlineStr">
         <is>
-          <t>fsa:NoncurrentDeferredTaxAssets</t>
+          <t>fsa:OtherProvisionsLiabilitiesShortterm</t>
         </is>
       </c>
       <c r="D6" s="38" t="n"/>
@@ -7347,7 +7349,7 @@
       <c r="F6" s="38" t="n"/>
       <c r="G6" s="38" t="n"/>
       <c r="H6" s="38" t="n">
-        <v>57200</v>
+        <v>400</v>
       </c>
       <c r="I6" s="39" t="inlineStr">
         <is>
@@ -7363,12 +7365,12 @@
       </c>
       <c r="B7" s="34" t="inlineStr">
         <is>
-          <t>fsa:OtherProvisionsLiabilitiesShortterm</t>
+          <t>fsa:PensionsAndSimilarLiabilitiesLiabilitiesLongterm</t>
         </is>
       </c>
       <c r="C7" s="34" t="inlineStr">
         <is>
-          <t>fsa:OtherProvisionsLiabilitiesShortterm</t>
+          <t>fsa:PensionsAndSimilarLiabilitiesLiabilitiesLongterm</t>
         </is>
       </c>
       <c r="D7" s="35" t="n"/>
@@ -7376,7 +7378,7 @@
       <c r="F7" s="35" t="n"/>
       <c r="G7" s="35" t="n"/>
       <c r="H7" s="35" t="n">
-        <v>400</v>
+        <v>10200</v>
       </c>
       <c r="I7" s="36" t="inlineStr">
         <is>
@@ -7392,12 +7394,12 @@
       </c>
       <c r="B8" s="37" t="inlineStr">
         <is>
-          <t>fsa:PensionsAndSimilarLiabilitiesLiabilitiesLongterm</t>
+          <t>fsa:ReserveForCurrentValueAdjustmentsOfCurrencyGains</t>
         </is>
       </c>
       <c r="C8" s="37" t="inlineStr">
         <is>
-          <t>fsa:PensionsAndSimilarLiabilitiesLiabilitiesLongterm</t>
+          <t>fsa:ReserveForCurrentValueAdjustmentsOfCurrencyGains</t>
         </is>
       </c>
       <c r="D8" s="38" t="n"/>
@@ -7405,7 +7407,7 @@
       <c r="F8" s="38" t="n"/>
       <c r="G8" s="38" t="n"/>
       <c r="H8" s="38" t="n">
-        <v>10200</v>
+        <v>-491500</v>
       </c>
       <c r="I8" s="39" t="inlineStr">
         <is>
@@ -7421,12 +7423,12 @@
       </c>
       <c r="B9" s="34" t="inlineStr">
         <is>
-          <t>fsa:ReserveForCurrentValueAdjustmentsOfCurrencyGains</t>
+          <t>fsa:ShorttermPayablesToAssociates</t>
         </is>
       </c>
       <c r="C9" s="34" t="inlineStr">
         <is>
-          <t>fsa:ReserveForCurrentValueAdjustmentsOfCurrencyGains</t>
+          <t>fsa:ShorttermPayablesToAssociates</t>
         </is>
       </c>
       <c r="D9" s="35" t="n"/>
@@ -7434,7 +7436,7 @@
       <c r="F9" s="35" t="n"/>
       <c r="G9" s="35" t="n"/>
       <c r="H9" s="35" t="n">
-        <v>-491500</v>
+        <v>0</v>
       </c>
       <c r="I9" s="36" t="inlineStr">
         <is>
@@ -7450,21 +7452,21 @@
       </c>
       <c r="B10" s="37" t="inlineStr">
         <is>
-          <t>fsa:ShorttermPayablesToAssociates</t>
+          <t>ifrs-full:AdjustmentsForReconcileProfitLoss</t>
         </is>
       </c>
       <c r="C10" s="37" t="inlineStr">
         <is>
-          <t>fsa:ShorttermPayablesToAssociates</t>
-        </is>
-      </c>
-      <c r="D10" s="38" t="n"/>
+          <t>ifrs-full:AdjustmentsForReconcileProfitLoss</t>
+        </is>
+      </c>
+      <c r="D10" s="38" t="n">
+        <v>8200</v>
+      </c>
       <c r="E10" s="38" t="n"/>
       <c r="F10" s="38" t="n"/>
       <c r="G10" s="38" t="n"/>
-      <c r="H10" s="38" t="n">
-        <v>0</v>
-      </c>
+      <c r="H10" s="38" t="n"/>
       <c r="I10" s="39" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
@@ -7479,19 +7481,23 @@
       </c>
       <c r="B11" s="34" t="inlineStr">
         <is>
-          <t>ifrs-full:AdjustmentsForReconcileProfitLoss</t>
+          <t>ifrs-full:CurrentGovernmentGrants</t>
         </is>
       </c>
       <c r="C11" s="34" t="inlineStr">
         <is>
-          <t>ifrs-full:AdjustmentsForReconcileProfitLoss</t>
+          <t>ifrs-full:CurrentGovernmentGrants</t>
         </is>
       </c>
       <c r="D11" s="35" t="n">
-        <v>8200</v>
-      </c>
-      <c r="E11" s="35" t="n"/>
-      <c r="F11" s="35" t="n"/>
+        <v>900</v>
+      </c>
+      <c r="E11" s="35" t="n">
+        <v>900</v>
+      </c>
+      <c r="F11" s="35" t="n">
+        <v>100</v>
+      </c>
       <c r="G11" s="35" t="n"/>
       <c r="H11" s="35" t="n"/>
       <c r="I11" s="36" t="inlineStr">
@@ -7508,24 +7514,20 @@
       </c>
       <c r="B12" s="37" t="inlineStr">
         <is>
-          <t>ifrs-full:CurrentGovernmentGrants</t>
+          <t>ifrs-full:GainsLossesOnHedgesOfNetInvestmentsInForeignOperationsBeforeTax</t>
         </is>
       </c>
       <c r="C12" s="37" t="inlineStr">
         <is>
-          <t>ifrs-full:CurrentGovernmentGrants</t>
-        </is>
-      </c>
-      <c r="D12" s="38" t="n">
-        <v>900</v>
-      </c>
-      <c r="E12" s="38" t="n">
-        <v>900</v>
-      </c>
-      <c r="F12" s="38" t="n">
-        <v>100</v>
-      </c>
-      <c r="G12" s="38" t="n"/>
+          <t>ifrs-full:GainsLossesOnHedgesOfNetInvestmentsInForeignOperationsBeforeTax</t>
+        </is>
+      </c>
+      <c r="D12" s="38" t="n"/>
+      <c r="E12" s="38" t="n"/>
+      <c r="F12" s="38" t="n"/>
+      <c r="G12" s="38" t="n">
+        <v>-151000</v>
+      </c>
       <c r="H12" s="38" t="n"/>
       <c r="I12" s="39" t="inlineStr">
         <is>
@@ -7541,20 +7543,22 @@
       </c>
       <c r="B13" s="34" t="inlineStr">
         <is>
-          <t>ifrs-full:GainsLossesOnHedgesOfNetInvestmentsInForeignOperationsBeforeTax</t>
+          <t>ifrs-full:GovernmentGrants</t>
         </is>
       </c>
       <c r="C13" s="34" t="inlineStr">
         <is>
-          <t>ifrs-full:GainsLossesOnHedgesOfNetInvestmentsInForeignOperationsBeforeTax</t>
+          <t>ifrs-full:GovernmentGrants</t>
         </is>
       </c>
       <c r="D13" s="35" t="n"/>
-      <c r="E13" s="35" t="n"/>
-      <c r="F13" s="35" t="n"/>
-      <c r="G13" s="35" t="n">
-        <v>-151000</v>
-      </c>
+      <c r="E13" s="35" t="n">
+        <v>500</v>
+      </c>
+      <c r="F13" s="35" t="n">
+        <v>300</v>
+      </c>
+      <c r="G13" s="35" t="n"/>
       <c r="H13" s="35" t="n"/>
       <c r="I13" s="36" t="inlineStr">
         <is>
@@ -7570,20 +7574,20 @@
       </c>
       <c r="B14" s="37" t="inlineStr">
         <is>
-          <t>ifrs-full:GovernmentGrants</t>
+          <t>ifrs-full:IncomeTaxRelatingToChangeInValueOfForeignCurrencyBasisSpreadsOfOtherComprehensiveIncome</t>
         </is>
       </c>
       <c r="C14" s="37" t="inlineStr">
         <is>
-          <t>ifrs-full:GovernmentGrants</t>
+          <t>ifrs-full:IncomeTaxRelatingToChangeInValueOfForeignCurrencyBasisSpreadsOfOtherComprehensiveIncome</t>
         </is>
       </c>
       <c r="D14" s="38" t="n"/>
       <c r="E14" s="38" t="n">
-        <v>500</v>
+        <v>-2900</v>
       </c>
       <c r="F14" s="38" t="n">
-        <v>300</v>
+        <v>800</v>
       </c>
       <c r="G14" s="38" t="n"/>
       <c r="H14" s="38" t="n"/>
@@ -7601,17 +7605,17 @@
       </c>
       <c r="B15" s="34" t="inlineStr">
         <is>
-          <t>ifrs-full:IncomeTaxRelatingToChangeInValueOfForeignCurrencyBasisSpreadsOfOtherComprehensiveIncome</t>
+          <t>ifrs-full:IncomeTaxRelatingToHedgesOfNetInvestmentsInForeignOperationsOfOtherComprehensiveIncome</t>
         </is>
       </c>
       <c r="C15" s="34" t="inlineStr">
         <is>
-          <t>ifrs-full:IncomeTaxRelatingToChangeInValueOfForeignCurrencyBasisSpreadsOfOtherComprehensiveIncome</t>
+          <t>ifrs-full:IncomeTaxRelatingToHedgesOfNetInvestmentsInForeignOperationsOfOtherComprehensiveIncome</t>
         </is>
       </c>
       <c r="D15" s="35" t="n"/>
       <c r="E15" s="35" t="n">
-        <v>-2900</v>
+        <v>0</v>
       </c>
       <c r="F15" s="35" t="n">
         <v>800</v>
@@ -7632,20 +7636,20 @@
       </c>
       <c r="B16" s="37" t="inlineStr">
         <is>
-          <t>ifrs-full:IncomeTaxRelatingToHedgesOfNetInvestmentsInForeignOperationsOfOtherComprehensiveIncome</t>
+          <t>ifrs-full:Machinery</t>
         </is>
       </c>
       <c r="C16" s="37" t="inlineStr">
         <is>
-          <t>ifrs-full:IncomeTaxRelatingToHedgesOfNetInvestmentsInForeignOperationsOfOtherComprehensiveIncome</t>
+          <t>ifrs-full:Machinery</t>
         </is>
       </c>
       <c r="D16" s="38" t="n"/>
       <c r="E16" s="38" t="n">
-        <v>0</v>
+        <v>717800</v>
       </c>
       <c r="F16" s="38" t="n">
-        <v>800</v>
+        <v>876400</v>
       </c>
       <c r="G16" s="38" t="n"/>
       <c r="H16" s="38" t="n"/>
@@ -7663,20 +7667,18 @@
       </c>
       <c r="B17" s="34" t="inlineStr">
         <is>
-          <t>ifrs-full:Machinery</t>
+          <t>ifrs-full:NoncurrentAssetsOrDisposalGroupsClassifiedAsHeldForSaleOrAsHeldForDistributionToOwners</t>
         </is>
       </c>
       <c r="C17" s="34" t="inlineStr">
         <is>
-          <t>ifrs-full:Machinery</t>
+          <t>ifrs-full:NoncurrentAssetsOrDisposalGroupsClassifiedAsHeldForSaleOrAsHeldForDistributionToOwners</t>
         </is>
       </c>
       <c r="D17" s="35" t="n"/>
-      <c r="E17" s="35" t="n">
-        <v>717800</v>
-      </c>
+      <c r="E17" s="35" t="n"/>
       <c r="F17" s="35" t="n">
-        <v>876400</v>
+        <v>91500</v>
       </c>
       <c r="G17" s="35" t="n"/>
       <c r="H17" s="35" t="n"/>
@@ -7694,19 +7696,19 @@
       </c>
       <c r="B18" s="37" t="inlineStr">
         <is>
-          <t>ifrs-full:NoncurrentAssetsOrDisposalGroupsClassifiedAsHeldForSaleOrAsHeldForDistributionToOwners</t>
+          <t>ifrs-full:NoncurrentGovernmentGrants</t>
         </is>
       </c>
       <c r="C18" s="37" t="inlineStr">
         <is>
-          <t>ifrs-full:NoncurrentAssetsOrDisposalGroupsClassifiedAsHeldForSaleOrAsHeldForDistributionToOwners</t>
-        </is>
-      </c>
-      <c r="D18" s="38" t="n"/>
+          <t>ifrs-full:NoncurrentGovernmentGrants</t>
+        </is>
+      </c>
+      <c r="D18" s="38" t="n">
+        <v>1500</v>
+      </c>
       <c r="E18" s="38" t="n"/>
-      <c r="F18" s="38" t="n">
-        <v>91500</v>
-      </c>
+      <c r="F18" s="38" t="n"/>
       <c r="G18" s="38" t="n"/>
       <c r="H18" s="38" t="n"/>
       <c r="I18" s="39" t="inlineStr">
@@ -7723,19 +7725,21 @@
       </c>
       <c r="B19" s="34" t="inlineStr">
         <is>
-          <t>ifrs-full:NoncurrentGovernmentGrants</t>
+          <t>ifrs-full:NoncurrentReceivablesDueFromRelatedParties</t>
         </is>
       </c>
       <c r="C19" s="34" t="inlineStr">
         <is>
-          <t>ifrs-full:NoncurrentGovernmentGrants</t>
-        </is>
-      </c>
-      <c r="D19" s="35" t="n">
-        <v>1500</v>
-      </c>
-      <c r="E19" s="35" t="n"/>
-      <c r="F19" s="35" t="n"/>
+          <t>ifrs-full:NoncurrentReceivablesDueFromRelatedParties</t>
+        </is>
+      </c>
+      <c r="D19" s="35" t="n"/>
+      <c r="E19" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="35" t="n">
+        <v>0</v>
+      </c>
       <c r="G19" s="35" t="n"/>
       <c r="H19" s="35" t="n"/>
       <c r="I19" s="36" t="inlineStr">
@@ -7752,20 +7756,20 @@
       </c>
       <c r="B20" s="37" t="inlineStr">
         <is>
-          <t>ifrs-full:NoncurrentReceivablesDueFromRelatedParties</t>
+          <t>ifrs-full:Prepayments</t>
         </is>
       </c>
       <c r="C20" s="37" t="inlineStr">
         <is>
-          <t>ifrs-full:NoncurrentReceivablesDueFromRelatedParties</t>
+          <t>ifrs-full:Prepayments</t>
         </is>
       </c>
       <c r="D20" s="38" t="n"/>
       <c r="E20" s="38" t="n">
-        <v>0</v>
+        <v>24300</v>
       </c>
       <c r="F20" s="38" t="n">
-        <v>0</v>
+        <v>25500</v>
       </c>
       <c r="G20" s="38" t="n"/>
       <c r="H20" s="38" t="n"/>
@@ -7783,86 +7787,24 @@
       </c>
       <c r="B21" s="34" t="inlineStr">
         <is>
-          <t>ifrs-full:Prepayments</t>
+          <t>ifrs-full:ReserveOfExchangeDifferencesOnTranslation</t>
         </is>
       </c>
       <c r="C21" s="34" t="inlineStr">
         <is>
-          <t>ifrs-full:Prepayments</t>
+          <t>ifrs-full:ReserveOfExchangeDifferencesOnTranslation</t>
         </is>
       </c>
       <c r="D21" s="35" t="n"/>
       <c r="E21" s="35" t="n">
-        <v>24300</v>
+        <v>-206000</v>
       </c>
       <c r="F21" s="35" t="n">
-        <v>25500</v>
+        <v>-149000</v>
       </c>
       <c r="G21" s="35" t="n"/>
       <c r="H21" s="35" t="n"/>
       <c r="I21" s="36" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="37" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B22" s="37" t="inlineStr">
-        <is>
-          <t>ifrs-full:ProceedsFromDisposalsOfPropertyPlantAndEquipmentIntangibleAssetsOtherThanGoodwillInvestmentPropertyAndOtherNoncurrentAssets</t>
-        </is>
-      </c>
-      <c r="C22" s="37" t="inlineStr">
-        <is>
-          <t>ifrs-full:ProceedsFromDisposalsOfPropertyPlantAndEquipmentIntangibleAssetsOtherThanGoodwillInvestmentPropertyAndOtherNoncurrentAssets</t>
-        </is>
-      </c>
-      <c r="D22" s="38" t="n"/>
-      <c r="E22" s="38" t="n">
-        <v>600</v>
-      </c>
-      <c r="F22" s="38" t="n">
-        <v>4700</v>
-      </c>
-      <c r="G22" s="38" t="n"/>
-      <c r="H22" s="38" t="n"/>
-      <c r="I22" s="39" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="30" customHeight="1">
-      <c r="A23" s="34" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B23" s="34" t="inlineStr">
-        <is>
-          <t>ifrs-full:ReserveOfExchangeDifferencesOnTranslation</t>
-        </is>
-      </c>
-      <c r="C23" s="34" t="inlineStr">
-        <is>
-          <t>ifrs-full:ReserveOfExchangeDifferencesOnTranslation</t>
-        </is>
-      </c>
-      <c r="D23" s="35" t="n"/>
-      <c r="E23" s="35" t="n">
-        <v>-206000</v>
-      </c>
-      <c r="F23" s="35" t="n">
-        <v>-149000</v>
-      </c>
-      <c r="G23" s="35" t="n"/>
-      <c r="H23" s="35" t="n"/>
-      <c r="I23" s="36" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
         </is>

--- a/filer/63049611_hartmann.xlsx
+++ b/filer/63049611_hartmann.xlsx
@@ -648,7 +648,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Regnskabsanalyse – Resultatopgørelse &amp; Balance (t.kr.)</t>
+          <t>Regnskabsanalyse – Resultatopgørelse &amp; Balance (t.kr.) · Klasse C-stor · Revision</t>
         </is>
       </c>
     </row>

--- a/filer/63049611_hartmann.xlsx
+++ b/filer/63049611_hartmann.xlsx
@@ -10,8 +10,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overblik_63049611" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="res_raw_63049611" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="balance_raw_63049611" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Simpel_funktion" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Noter_info" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pengestrom_raw_63049611" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Simpel_funktion" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Noter_info" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -204,9 +205,9 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -628,7 +629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L94"/>
+  <dimension ref="A1:L101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -648,7 +649,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Regnskabsanalyse – Resultatopgørelse &amp; Balance (t.kr.) · Klasse C-stor · Revision</t>
+          <t>Regnskabsanalyse – Resultatopgørelse &amp; Balance (t.kr.) · Klasse C-stor · Independent Auditor’s Report</t>
         </is>
       </c>
     </row>
@@ -662,7 +663,7 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Indekstal (2020=100)</t>
+          <t>Indekstal (2021=100)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -677,35 +678,35 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
@@ -1435,35 +1436,35 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="21" ht="16" customHeight="1">
@@ -2769,35 +2770,35 @@
         </is>
       </c>
       <c r="B49" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C49" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D49" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G49" t="inlineStr"/>
       <c r="H49" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="I49" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="K49" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="L49" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="50" ht="16" customHeight="1">
@@ -4151,19 +4152,19 @@
         </is>
       </c>
       <c r="B79" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C79" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D79" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E79" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="80" ht="16" customHeight="1">
@@ -4269,19 +4270,19 @@
         </is>
       </c>
       <c r="B83" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C83" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E83" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F83" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="84" ht="16" customHeight="1">
@@ -4578,6 +4579,148 @@
       </c>
       <c r="F94" s="13">
         <f>IFERROR($F$34/($F$56+$F$63)*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="15" t="inlineStr">
+        <is>
+          <t>PENGESTRØMSOPGØRELSE t.kr.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra driftsaktivitet</t>
+        </is>
+      </c>
+      <c r="B97" s="17">
+        <f>'pengestrom_raw_63049611'!$B$2</f>
+        <v/>
+      </c>
+      <c r="C97" s="17">
+        <f>'pengestrom_raw_63049611'!$C$2</f>
+        <v/>
+      </c>
+      <c r="D97" s="17">
+        <f>'pengestrom_raw_63049611'!$D$2</f>
+        <v/>
+      </c>
+      <c r="E97" s="17">
+        <f>'pengestrom_raw_63049611'!$E$2</f>
+        <v/>
+      </c>
+      <c r="F97" s="17">
+        <f>'pengestrom_raw_63049611'!$F$2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra investeringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B98" s="17">
+        <f>'pengestrom_raw_63049611'!$B$3</f>
+        <v/>
+      </c>
+      <c r="C98" s="17">
+        <f>'pengestrom_raw_63049611'!$C$3</f>
+        <v/>
+      </c>
+      <c r="D98" s="17">
+        <f>'pengestrom_raw_63049611'!$D$3</f>
+        <v/>
+      </c>
+      <c r="E98" s="17">
+        <f>'pengestrom_raw_63049611'!$E$3</f>
+        <v/>
+      </c>
+      <c r="F98" s="17">
+        <f>'pengestrom_raw_63049611'!$F$3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra finansieringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B99" s="17">
+        <f>'pengestrom_raw_63049611'!$B$4</f>
+        <v/>
+      </c>
+      <c r="C99" s="17">
+        <f>'pengestrom_raw_63049611'!$C$4</f>
+        <v/>
+      </c>
+      <c r="D99" s="17">
+        <f>'pengestrom_raw_63049611'!$D$4</f>
+        <v/>
+      </c>
+      <c r="E99" s="17">
+        <f>'pengestrom_raw_63049611'!$E$4</f>
+        <v/>
+      </c>
+      <c r="F99" s="17">
+        <f>'pengestrom_raw_63049611'!$F$4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="16" t="inlineStr">
+        <is>
+          <t>Årets pengestrøm (rapporteret)</t>
+        </is>
+      </c>
+      <c r="B100" s="17">
+        <f>'pengestrom_raw_63049611'!$B$5</f>
+        <v/>
+      </c>
+      <c r="C100" s="17">
+        <f>'pengestrom_raw_63049611'!$C$5</f>
+        <v/>
+      </c>
+      <c r="D100" s="17">
+        <f>'pengestrom_raw_63049611'!$D$5</f>
+        <v/>
+      </c>
+      <c r="E100" s="17">
+        <f>'pengestrom_raw_63049611'!$E$5</f>
+        <v/>
+      </c>
+      <c r="F100" s="17">
+        <f>'pengestrom_raw_63049611'!$F$5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="16" t="inlineStr">
+        <is>
+          <t>Krydstjek: drift + inv. + fin. = årets pengestrøm</t>
+        </is>
+      </c>
+      <c r="B101">
+        <f>IF(ABS(('pengestrom_raw_63049611'!$B$2+'pengestrom_raw_63049611'!$B$3+'pengestrom_raw_63049611'!$B$4)-'pengestrom_raw_63049611'!$B$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_63049611'!$B$2+'pengestrom_raw_63049611'!$B$3+'pengestrom_raw_63049611'!$B$4)-'pengestrom_raw_63049611'!$B$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="C101">
+        <f>IF(ABS(('pengestrom_raw_63049611'!$C$2+'pengestrom_raw_63049611'!$C$3+'pengestrom_raw_63049611'!$C$4)-'pengestrom_raw_63049611'!$C$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_63049611'!$C$2+'pengestrom_raw_63049611'!$C$3+'pengestrom_raw_63049611'!$C$4)-'pengestrom_raw_63049611'!$C$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="D101">
+        <f>IF(ABS(('pengestrom_raw_63049611'!$D$2+'pengestrom_raw_63049611'!$D$3+'pengestrom_raw_63049611'!$D$4)-'pengestrom_raw_63049611'!$D$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_63049611'!$D$2+'pengestrom_raw_63049611'!$D$3+'pengestrom_raw_63049611'!$D$4)-'pengestrom_raw_63049611'!$D$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="E101">
+        <f>IF(ABS(('pengestrom_raw_63049611'!$E$2+'pengestrom_raw_63049611'!$E$3+'pengestrom_raw_63049611'!$E$4)-'pengestrom_raw_63049611'!$E$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_63049611'!$E$2+'pengestrom_raw_63049611'!$E$3+'pengestrom_raw_63049611'!$E$4)-'pengestrom_raw_63049611'!$E$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="F101">
+        <f>IF(ABS(('pengestrom_raw_63049611'!$F$2+'pengestrom_raw_63049611'!$F$3+'pengestrom_raw_63049611'!$F$4)-'pengestrom_raw_63049611'!$F$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_63049611'!$F$2+'pengestrom_raw_63049611'!$F$3+'pengestrom_raw_63049611'!$F$4)-'pengestrom_raw_63049611'!$F$5,"+#,##0;-#,##0"))</f>
         <v/>
       </c>
     </row>
@@ -4610,336 +4753,346 @@
         </is>
       </c>
       <c r="B1" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C1" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D1" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E1" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F1" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="15" t="inlineStr">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>Nettoomsætning</t>
         </is>
       </c>
-      <c r="B2" s="16" t="n">
-        <v>2567400</v>
-      </c>
-      <c r="C2" s="16" t="n">
+      <c r="B2" s="17" t="n">
         <v>2666100</v>
       </c>
-      <c r="D2" s="16" t="n">
+      <c r="C2" s="17" t="n">
         <v>3350100</v>
       </c>
-      <c r="E2" s="16" t="n">
+      <c r="D2" s="17" t="n">
         <v>3307600</v>
       </c>
-      <c r="F2" s="16" t="n">
+      <c r="E2" s="17" t="n">
         <v>3810300</v>
       </c>
+      <c r="F2" s="17" t="n">
+        <v>4145000</v>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="15" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>Produktionsomkostninger</t>
         </is>
       </c>
-      <c r="B3" s="16" t="n"/>
-      <c r="C3" s="16" t="n">
+      <c r="B3" s="17" t="n">
         <v>1961300</v>
       </c>
-      <c r="D3" s="16" t="n">
+      <c r="C3" s="17" t="n">
         <v>2535100</v>
       </c>
-      <c r="E3" s="16" t="n"/>
-      <c r="F3" s="16" t="n">
+      <c r="D3" s="17" t="n"/>
+      <c r="E3" s="17" t="n">
         <v>2574100</v>
       </c>
+      <c r="F3" s="17" t="n">
+        <v>2798300</v>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="17" t="inlineStr">
+      <c r="A4" s="15" t="inlineStr">
         <is>
           <t>Bruttoresultat</t>
         </is>
       </c>
-      <c r="B4" s="16" t="n">
-        <v>910000</v>
-      </c>
-      <c r="C4" s="16" t="n">
+      <c r="B4" s="17" t="n">
         <v>704800</v>
       </c>
-      <c r="D4" s="16" t="n">
+      <c r="C4" s="17" t="n">
         <v>815000</v>
       </c>
-      <c r="E4" s="16" t="n">
+      <c r="D4" s="17" t="n">
         <v>1035000</v>
       </c>
-      <c r="F4" s="16" t="n">
+      <c r="E4" s="17" t="n">
         <v>1236200</v>
       </c>
+      <c r="F4" s="17" t="n">
+        <v>1346700</v>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>Salgs- og distributionsomkostninger</t>
         </is>
       </c>
-      <c r="B5" s="16" t="n"/>
-      <c r="C5" s="16" t="n"/>
-      <c r="D5" s="16" t="n"/>
-      <c r="E5" s="16" t="n"/>
-      <c r="F5" s="16" t="n">
+      <c r="B5" s="17" t="n"/>
+      <c r="C5" s="17" t="n"/>
+      <c r="D5" s="17" t="n"/>
+      <c r="E5" s="17" t="n">
         <v>433600</v>
       </c>
+      <c r="F5" s="17" t="n">
+        <v>443800</v>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>Administrationsomkostninger</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n">
-        <v>108800</v>
-      </c>
-      <c r="C6" s="16" t="n">
+      <c r="B6" s="17" t="n">
         <v>113400</v>
       </c>
-      <c r="D6" s="16" t="n">
+      <c r="C6" s="17" t="n">
         <v>149400</v>
       </c>
-      <c r="E6" s="16" t="n">
+      <c r="D6" s="17" t="n">
         <v>160200</v>
       </c>
-      <c r="F6" s="16" t="n">
+      <c r="E6" s="17" t="n">
         <v>229100</v>
       </c>
+      <c r="F6" s="17" t="n">
+        <v>237400</v>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>Andre driftsindtægter</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n"/>
-      <c r="C7" s="16" t="n"/>
-      <c r="D7" s="16" t="n">
+      <c r="B7" s="17" t="n"/>
+      <c r="C7" s="17" t="n">
         <v>8200</v>
       </c>
-      <c r="E7" s="16" t="n">
+      <c r="D7" s="17" t="n">
         <v>-2900</v>
       </c>
-      <c r="F7" s="16" t="n"/>
+      <c r="E7" s="17" t="n">
+        <v>-3500</v>
+      </c>
+      <c r="F7" s="17" t="n">
+        <v>400</v>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>Andre driftsomkostninger</t>
         </is>
       </c>
-      <c r="B8" s="16" t="n"/>
-      <c r="C8" s="16" t="n"/>
-      <c r="D8" s="16" t="n"/>
-      <c r="E8" s="16" t="n"/>
-      <c r="F8" s="16" t="n">
+      <c r="B8" s="17" t="n"/>
+      <c r="C8" s="17" t="n"/>
+      <c r="D8" s="17" t="n"/>
+      <c r="E8" s="17" t="n">
         <v>3500</v>
       </c>
+      <c r="F8" s="17" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="inlineStr">
+      <c r="A9" s="15" t="inlineStr">
         <is>
           <t>Resultat af primær drift</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n">
-        <v>424100</v>
-      </c>
-      <c r="C9" s="16" t="n"/>
-      <c r="D9" s="16" t="n"/>
-      <c r="E9" s="16" t="n">
+      <c r="B9" s="17" t="n"/>
+      <c r="C9" s="17" t="n"/>
+      <c r="D9" s="17" t="n">
         <v>331000</v>
       </c>
-      <c r="F9" s="16" t="n">
+      <c r="E9" s="17" t="n">
         <v>570000</v>
       </c>
+      <c r="F9" s="17" t="n">
+        <v>665900</v>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>Indtægter af kapitalandele, dattervirksomheder</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n"/>
-      <c r="C10" s="16" t="n">
+      <c r="B10" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="D10" s="16" t="n">
+      <c r="C10" s="17" t="n">
         <v>200</v>
       </c>
-      <c r="E10" s="16" t="n"/>
-      <c r="F10" s="16" t="n"/>
+      <c r="D10" s="17" t="n"/>
+      <c r="E10" s="17" t="n"/>
+      <c r="F10" s="17" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>Finansielle indtægter</t>
         </is>
       </c>
-      <c r="B11" s="16" t="n">
-        <v>13900</v>
-      </c>
-      <c r="C11" s="16" t="n">
+      <c r="B11" s="17" t="n">
         <v>36900</v>
       </c>
-      <c r="D11" s="16" t="n">
+      <c r="C11" s="17" t="n">
         <v>27200</v>
       </c>
-      <c r="E11" s="16" t="n">
+      <c r="D11" s="17" t="n">
         <v>44900</v>
       </c>
-      <c r="F11" s="16" t="n">
+      <c r="E11" s="17" t="n">
         <v>57200</v>
       </c>
+      <c r="F11" s="17" t="n">
+        <v>27500</v>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>Finansielle omkostninger</t>
         </is>
       </c>
-      <c r="B12" s="16" t="n">
-        <v>79000</v>
-      </c>
-      <c r="C12" s="16" t="n">
+      <c r="B12" s="17" t="n">
         <v>46300</v>
       </c>
-      <c r="D12" s="16" t="n">
+      <c r="C12" s="17" t="n">
         <v>98900</v>
       </c>
-      <c r="E12" s="16" t="n">
+      <c r="D12" s="17" t="n">
         <v>123700</v>
       </c>
-      <c r="F12" s="16" t="n">
+      <c r="E12" s="17" t="n">
         <v>85600</v>
       </c>
+      <c r="F12" s="17" t="n">
+        <v>91500</v>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="17" t="inlineStr">
+      <c r="A13" s="15" t="inlineStr">
         <is>
           <t>Finansielle poster, netto</t>
         </is>
       </c>
-      <c r="B13" s="16" t="n"/>
-      <c r="C13" s="16" t="n"/>
-      <c r="D13" s="16" t="n"/>
-      <c r="E13" s="16" t="n"/>
-      <c r="F13" s="16" t="n"/>
+      <c r="B13" s="17" t="n"/>
+      <c r="C13" s="17" t="n"/>
+      <c r="D13" s="17" t="n"/>
+      <c r="E13" s="17" t="n"/>
+      <c r="F13" s="17" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="17" t="inlineStr">
+      <c r="A14" s="15" t="inlineStr">
         <is>
           <t>Resultat før skat</t>
         </is>
       </c>
-      <c r="B14" s="16" t="n">
-        <v>359000</v>
-      </c>
-      <c r="C14" s="16" t="n">
+      <c r="B14" s="17" t="n">
         <v>105500</v>
       </c>
-      <c r="D14" s="16" t="n">
+      <c r="C14" s="17" t="n">
         <v>132400</v>
       </c>
-      <c r="E14" s="16" t="n">
+      <c r="D14" s="17" t="n">
         <v>252300</v>
       </c>
-      <c r="F14" s="16" t="n">
+      <c r="E14" s="17" t="n">
         <v>541600</v>
       </c>
+      <c r="F14" s="17" t="n">
+        <v>601900</v>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="15" t="inlineStr">
+      <c r="A15" s="16" t="inlineStr">
         <is>
           <t>Skat af årets resultat</t>
         </is>
       </c>
-      <c r="B15" s="16" t="n"/>
-      <c r="C15" s="16" t="n">
+      <c r="B15" s="17" t="n">
         <v>31000</v>
       </c>
-      <c r="D15" s="16" t="n">
+      <c r="C15" s="17" t="n">
         <v>71100</v>
       </c>
-      <c r="E15" s="16" t="n"/>
-      <c r="F15" s="16" t="n">
+      <c r="D15" s="17" t="n"/>
+      <c r="E15" s="17" t="n">
         <v>124700</v>
       </c>
+      <c r="F15" s="17" t="n">
+        <v>154400</v>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="17" t="inlineStr">
+      <c r="A16" s="15" t="inlineStr">
         <is>
           <t>Årets resultat</t>
         </is>
       </c>
-      <c r="B16" s="16" t="n">
-        <v>273900</v>
-      </c>
-      <c r="C16" s="16" t="n">
+      <c r="B16" s="17" t="n">
         <v>74500</v>
       </c>
-      <c r="D16" s="16" t="n">
+      <c r="C16" s="17" t="n">
         <v>61300</v>
       </c>
-      <c r="E16" s="16" t="n">
+      <c r="D16" s="17" t="n">
         <v>158700</v>
       </c>
-      <c r="F16" s="16" t="n">
+      <c r="E16" s="17" t="n">
         <v>416900</v>
       </c>
+      <c r="F16" s="17" t="n">
+        <v>447500</v>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>Gns. antal medarbejdere</t>
         </is>
       </c>
-      <c r="B17" s="16" t="n"/>
-      <c r="C17" s="16" t="n"/>
-      <c r="D17" s="16" t="n"/>
-      <c r="E17" s="16" t="n">
+      <c r="B17" s="17" t="n"/>
+      <c r="C17" s="17" t="n"/>
+      <c r="D17" s="17" t="n">
         <v>2796</v>
       </c>
-      <c r="F17" s="16" t="n">
+      <c r="E17" s="17" t="n">
         <v>3064</v>
       </c>
+      <c r="F17" s="17" t="n">
+        <v>3296</v>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="inlineStr">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>Investering i materielle anlægsaktiver</t>
         </is>
       </c>
-      <c r="B18" s="16" t="n">
-        <v>-320900</v>
-      </c>
-      <c r="C18" s="16" t="n">
+      <c r="B18" s="17" t="n">
         <v>370700</v>
       </c>
-      <c r="D18" s="16" t="n">
+      <c r="C18" s="17" t="n">
         <v>163500</v>
       </c>
-      <c r="E18" s="16" t="n">
+      <c r="D18" s="17" t="n">
         <v>-268500</v>
       </c>
-      <c r="F18" s="16" t="n"/>
+      <c r="E18" s="17" t="n"/>
+      <c r="F18" s="17" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4970,997 +5123,1015 @@
         </is>
       </c>
       <c r="B1" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C1" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D1" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E1" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F1" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="15" t="inlineStr">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>Udviklingsprojekter</t>
         </is>
       </c>
-      <c r="B2" s="16" t="n"/>
-      <c r="C2" s="16" t="n"/>
-      <c r="D2" s="16" t="n"/>
-      <c r="E2" s="16" t="n">
+      <c r="B2" s="17" t="n"/>
+      <c r="C2" s="17" t="n"/>
+      <c r="D2" s="17" t="n">
         <v>44700</v>
       </c>
-      <c r="F2" s="16" t="n"/>
+      <c r="E2" s="17" t="n"/>
+      <c r="F2" s="17" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="15" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>Patenter, varemærker mv.</t>
         </is>
       </c>
-      <c r="B3" s="16" t="n"/>
-      <c r="C3" s="16" t="n"/>
-      <c r="D3" s="16" t="n"/>
-      <c r="E3" s="16" t="n"/>
-      <c r="F3" s="16" t="n"/>
+      <c r="B3" s="17" t="n"/>
+      <c r="C3" s="17" t="n"/>
+      <c r="D3" s="17" t="n"/>
+      <c r="E3" s="17" t="n"/>
+      <c r="F3" s="17" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>Goodwill</t>
         </is>
       </c>
-      <c r="B4" s="16" t="n">
-        <v>90700</v>
-      </c>
-      <c r="C4" s="16" t="n">
+      <c r="B4" s="17" t="n">
         <v>108400</v>
       </c>
-      <c r="D4" s="16" t="n">
+      <c r="C4" s="17" t="n">
         <v>54400</v>
       </c>
-      <c r="E4" s="16" t="n">
+      <c r="D4" s="17" t="n">
         <v>10700</v>
       </c>
-      <c r="F4" s="16" t="n"/>
+      <c r="E4" s="17" t="n"/>
+      <c r="F4" s="17" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="inlineStr">
+      <c r="A5" s="15" t="inlineStr">
         <is>
           <t>Immaterielle anlægsaktiver</t>
         </is>
       </c>
-      <c r="B5" s="16" t="n">
+      <c r="B5" s="17" t="n">
+        <v>61600</v>
+      </c>
+      <c r="C5" s="17" t="n">
+        <v>60300</v>
+      </c>
+      <c r="D5" s="17" t="n">
+        <v>55400</v>
+      </c>
+      <c r="E5" s="17" t="n">
+        <v>31700</v>
+      </c>
+      <c r="F5" s="17" t="n">
+        <v>17800</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="16" t="inlineStr">
+        <is>
+          <t>Grunde og bygninger</t>
+        </is>
+      </c>
+      <c r="B6" s="17" t="n">
+        <v>398400</v>
+      </c>
+      <c r="C6" s="17" t="n">
+        <v>362100</v>
+      </c>
+      <c r="D6" s="17" t="n">
+        <v>330500</v>
+      </c>
+      <c r="E6" s="17" t="n">
+        <v>372900</v>
+      </c>
+      <c r="F6" s="17" t="n">
+        <v>389000</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="16" t="inlineStr">
+        <is>
+          <t>Produktionsanlæg og maskiner</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="n"/>
+      <c r="C7" s="17" t="n"/>
+      <c r="D7" s="17" t="n"/>
+      <c r="E7" s="17" t="n">
+        <v>1072000</v>
+      </c>
+      <c r="F7" s="17" t="n">
+        <v>1193700</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="16" t="inlineStr">
+        <is>
+          <t>Driftsmateriel og inventar</t>
+        </is>
+      </c>
+      <c r="B8" s="17" t="n"/>
+      <c r="C8" s="17" t="n"/>
+      <c r="D8" s="17" t="n"/>
+      <c r="E8" s="17" t="n">
+        <v>36800</v>
+      </c>
+      <c r="F8" s="17" t="n">
         <v>37200</v>
       </c>
-      <c r="C5" s="16" t="n">
-        <v>61600</v>
-      </c>
-      <c r="D5" s="16" t="n">
+    </row>
+    <row r="9">
+      <c r="A9" s="16" t="inlineStr">
+        <is>
+          <t>Indretning af lejede lokaler</t>
+        </is>
+      </c>
+      <c r="B9" s="17" t="n"/>
+      <c r="C9" s="17" t="n"/>
+      <c r="D9" s="17" t="n"/>
+      <c r="E9" s="17" t="n"/>
+      <c r="F9" s="17" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="16" t="inlineStr">
+        <is>
+          <t>Forudbetaling og anlægsaktiver under opførelse</t>
+        </is>
+      </c>
+      <c r="B10" s="17" t="n">
+        <v>354200</v>
+      </c>
+      <c r="C10" s="17" t="n">
+        <v>112700</v>
+      </c>
+      <c r="D10" s="17" t="n"/>
+      <c r="E10" s="17" t="n">
+        <v>174300</v>
+      </c>
+      <c r="F10" s="17" t="n">
+        <v>287200</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>Materielle anlægsaktiver</t>
+        </is>
+      </c>
+      <c r="B11" s="17" t="n">
+        <v>21400</v>
+      </c>
+      <c r="C11" s="17" t="n">
+        <v>20700</v>
+      </c>
+      <c r="D11" s="17" t="n">
+        <v>1388400</v>
+      </c>
+      <c r="E11" s="17" t="n">
+        <v>1656000</v>
+      </c>
+      <c r="F11" s="17" t="n">
+        <v>1907100</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="16" t="inlineStr">
+        <is>
+          <t>Kapitalandele, dattervirksomheder</t>
+        </is>
+      </c>
+      <c r="B12" s="17" t="n"/>
+      <c r="C12" s="17" t="n"/>
+      <c r="D12" s="17" t="n"/>
+      <c r="E12" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="16" t="inlineStr">
+        <is>
+          <t>Deposita</t>
+        </is>
+      </c>
+      <c r="B13" s="17" t="n">
+        <v>2600</v>
+      </c>
+      <c r="C13" s="17" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D13" s="17" t="n"/>
+      <c r="E13" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="15" t="inlineStr">
+        <is>
+          <t>Finansielle anlægsaktiver</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="n"/>
+      <c r="C14" s="17" t="n"/>
+      <c r="D14" s="17" t="n"/>
+      <c r="E14" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="17" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>Anlægsaktiver</t>
+        </is>
+      </c>
+      <c r="B15" s="17" t="n">
+        <v>1812600</v>
+      </c>
+      <c r="C15" s="17" t="n">
+        <v>1630800</v>
+      </c>
+      <c r="D15" s="17" t="n">
+        <v>1577900</v>
+      </c>
+      <c r="E15" s="17" t="n">
+        <v>1744900</v>
+      </c>
+      <c r="F15" s="17" t="n">
+        <v>1976700</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>Varebeholdninger</t>
+        </is>
+      </c>
+      <c r="B16" s="17" t="n">
+        <v>299900</v>
+      </c>
+      <c r="C16" s="17" t="n">
+        <v>327600</v>
+      </c>
+      <c r="D16" s="17" t="n">
+        <v>340400</v>
+      </c>
+      <c r="E16" s="17" t="n">
+        <v>389000</v>
+      </c>
+      <c r="F16" s="17" t="n">
+        <v>442600</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="16" t="inlineStr">
+        <is>
+          <t>Tilgodehavender fra salg og tjenesteydelser</t>
+        </is>
+      </c>
+      <c r="B17" s="17" t="n">
+        <v>396200</v>
+      </c>
+      <c r="C17" s="17" t="n">
+        <v>459500</v>
+      </c>
+      <c r="D17" s="17" t="n">
+        <v>457000</v>
+      </c>
+      <c r="E17" s="17" t="n">
+        <v>527100</v>
+      </c>
+      <c r="F17" s="17" t="n">
+        <v>501700</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="16" t="inlineStr">
+        <is>
+          <t>Tilgodehavender hos tilknyttede virksomheder</t>
+        </is>
+      </c>
+      <c r="B18" s="17" t="n"/>
+      <c r="C18" s="17" t="n"/>
+      <c r="D18" s="17" t="n"/>
+      <c r="E18" s="17" t="n">
+        <v>102800</v>
+      </c>
+      <c r="F18" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="16" t="inlineStr">
+        <is>
+          <t>Andre tilgodehavender</t>
+        </is>
+      </c>
+      <c r="B19" s="17" t="n">
+        <v>14200</v>
+      </c>
+      <c r="C19" s="17" t="n">
+        <v>17500</v>
+      </c>
+      <c r="D19" s="17" t="n"/>
+      <c r="E19" s="17" t="n">
+        <v>94300</v>
+      </c>
+      <c r="F19" s="17" t="n">
+        <v>103200</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="16" t="inlineStr">
+        <is>
+          <t>Periodeafgrænsningsposter (aktiver)</t>
+        </is>
+      </c>
+      <c r="B20" s="17" t="n"/>
+      <c r="C20" s="17" t="n"/>
+      <c r="D20" s="17" t="n">
+        <v>37600</v>
+      </c>
+      <c r="E20" s="17" t="n">
+        <v>48100</v>
+      </c>
+      <c r="F20" s="17" t="n">
+        <v>33800</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="16" t="inlineStr">
+        <is>
+          <t>Udskudt skatteaktiv</t>
+        </is>
+      </c>
+      <c r="B21" s="17" t="n">
+        <v>62000</v>
+      </c>
+      <c r="C21" s="17" t="n">
+        <v>63200</v>
+      </c>
+      <c r="D21" s="17" t="n">
+        <v>54700</v>
+      </c>
+      <c r="E21" s="17" t="n">
+        <v>57200</v>
+      </c>
+      <c r="F21" s="17" t="n">
+        <v>51800</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="16" t="inlineStr">
+        <is>
+          <t>Tilgodehavende skat hos tilknyttede virksomheder</t>
+        </is>
+      </c>
+      <c r="B22" s="17" t="n"/>
+      <c r="C22" s="17" t="n"/>
+      <c r="D22" s="17" t="n"/>
+      <c r="E22" s="17" t="n"/>
+      <c r="F22" s="17" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="16" t="inlineStr">
+        <is>
+          <t>Kortfristede skattetilgodehavender</t>
+        </is>
+      </c>
+      <c r="B23" s="17" t="n">
+        <v>28100</v>
+      </c>
+      <c r="C23" s="17" t="n">
+        <v>24200</v>
+      </c>
+      <c r="D23" s="17" t="n">
+        <v>13400</v>
+      </c>
+      <c r="E23" s="17" t="n">
+        <v>700</v>
+      </c>
+      <c r="F23" s="17" t="n">
+        <v>7100</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="15" t="inlineStr">
+        <is>
+          <t>Tilgodehavender</t>
+        </is>
+      </c>
+      <c r="B24" s="17" t="n">
+        <v>125200</v>
+      </c>
+      <c r="C24" s="17" t="n">
+        <v>209200</v>
+      </c>
+      <c r="D24" s="17" t="n">
+        <v>108900</v>
+      </c>
+      <c r="E24" s="17" t="n"/>
+      <c r="F24" s="17" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="16" t="inlineStr">
+        <is>
+          <t>Værdipapirer</t>
+        </is>
+      </c>
+      <c r="B25" s="17" t="n"/>
+      <c r="C25" s="17" t="n"/>
+      <c r="D25" s="17" t="n"/>
+      <c r="E25" s="17" t="n"/>
+      <c r="F25" s="17" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="16" t="inlineStr">
+        <is>
+          <t>Likvide beholdninger</t>
+        </is>
+      </c>
+      <c r="B26" s="17" t="n">
+        <v>144800</v>
+      </c>
+      <c r="C26" s="17" t="n">
+        <v>180200</v>
+      </c>
+      <c r="D26" s="17" t="n">
+        <v>298200</v>
+      </c>
+      <c r="E26" s="17" t="n">
+        <v>250300</v>
+      </c>
+      <c r="F26" s="17" t="n">
+        <v>250700</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="15" t="inlineStr">
+        <is>
+          <t>Omsætningsaktiver</t>
+        </is>
+      </c>
+      <c r="B27" s="17" t="n">
+        <v>991600</v>
+      </c>
+      <c r="C27" s="17" t="n">
+        <v>1226200</v>
+      </c>
+      <c r="D27" s="17" t="n">
+        <v>1143700</v>
+      </c>
+      <c r="E27" s="17" t="n">
+        <v>1412300</v>
+      </c>
+      <c r="F27" s="17" t="n">
+        <v>1339100</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="15" t="inlineStr">
+        <is>
+          <t>Aktiver</t>
+        </is>
+      </c>
+      <c r="B28" s="17" t="n">
+        <v>2804200</v>
+      </c>
+      <c r="C28" s="17" t="n">
+        <v>2948500</v>
+      </c>
+      <c r="D28" s="17" t="n">
+        <v>2723500</v>
+      </c>
+      <c r="E28" s="17" t="n">
+        <v>3157200</v>
+      </c>
+      <c r="F28" s="17" t="n">
+        <v>3315800</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="16" t="inlineStr">
+        <is>
+          <t>Selskabskapital</t>
+        </is>
+      </c>
+      <c r="B29" s="17" t="n">
+        <v>140300</v>
+      </c>
+      <c r="C29" s="17" t="n">
+        <v>140300</v>
+      </c>
+      <c r="D29" s="17" t="n">
+        <v>140300</v>
+      </c>
+      <c r="E29" s="17" t="n">
+        <v>140300</v>
+      </c>
+      <c r="F29" s="17" t="n">
+        <v>138300</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="16" t="inlineStr">
+        <is>
+          <t>Reserve for nettoopskrivning (indre værdis metode)</t>
+        </is>
+      </c>
+      <c r="B30" s="17" t="n"/>
+      <c r="C30" s="17" t="n"/>
+      <c r="D30" s="17" t="n"/>
+      <c r="E30" s="17" t="n"/>
+      <c r="F30" s="17" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="16" t="inlineStr">
+        <is>
+          <t>Reserve for udviklingsomkostninger</t>
+        </is>
+      </c>
+      <c r="B31" s="17" t="n"/>
+      <c r="C31" s="17" t="n"/>
+      <c r="D31" s="17" t="n"/>
+      <c r="E31" s="17" t="n"/>
+      <c r="F31" s="17" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="16" t="inlineStr">
+        <is>
+          <t>Reserve for sikringstransaktioner</t>
+        </is>
+      </c>
+      <c r="B32" s="17" t="n"/>
+      <c r="C32" s="17" t="n"/>
+      <c r="D32" s="17" t="n"/>
+      <c r="E32" s="17" t="n">
+        <v>-4500</v>
+      </c>
+      <c r="F32" s="17" t="n">
+        <v>-21400</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="16" t="inlineStr">
+        <is>
+          <t>Andre reserver</t>
+        </is>
+      </c>
+      <c r="B33" s="17" t="n">
+        <v>-7800</v>
+      </c>
+      <c r="C33" s="17" t="n">
+        <v>-400</v>
+      </c>
+      <c r="D33" s="17" t="n">
+        <v>-12200</v>
+      </c>
+      <c r="E33" s="17" t="n"/>
+      <c r="F33" s="17" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="16" t="inlineStr">
+        <is>
+          <t>Overført resultat</t>
+        </is>
+      </c>
+      <c r="B34" s="17" t="n">
+        <v>1270000</v>
+      </c>
+      <c r="C34" s="17" t="n">
+        <v>1230900</v>
+      </c>
+      <c r="D34" s="17" t="n">
+        <v>1344800</v>
+      </c>
+      <c r="E34" s="17" t="n">
+        <v>1921900</v>
+      </c>
+      <c r="F34" s="17" t="n">
+        <v>2173500</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="15" t="inlineStr">
+        <is>
+          <t>Egenkapital i alt</t>
+        </is>
+      </c>
+      <c r="B35" s="17" t="n">
+        <v>1196500</v>
+      </c>
+      <c r="C35" s="17" t="n">
+        <v>1221800</v>
+      </c>
+      <c r="D35" s="17" t="n">
+        <v>1224600</v>
+      </c>
+      <c r="E35" s="17" t="n">
+        <v>1672700</v>
+      </c>
+      <c r="F35" s="17" t="n">
+        <v>1902200</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="16" t="inlineStr">
+        <is>
+          <t>Hensættelse til udskudt skat</t>
+        </is>
+      </c>
+      <c r="B36" s="17" t="n">
+        <v>39700</v>
+      </c>
+      <c r="C36" s="17" t="n">
         <v>60300</v>
       </c>
-      <c r="E5" s="16" t="n">
-        <v>55400</v>
-      </c>
-      <c r="F5" s="16" t="n">
-        <v>31700</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="15" t="inlineStr">
-        <is>
-          <t>Grunde og bygninger</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="n">
-        <v>326100</v>
-      </c>
-      <c r="C6" s="16" t="n">
-        <v>398400</v>
-      </c>
-      <c r="D6" s="16" t="n">
-        <v>362100</v>
-      </c>
-      <c r="E6" s="16" t="n">
-        <v>330500</v>
-      </c>
-      <c r="F6" s="16" t="n">
-        <v>372900</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="15" t="inlineStr">
-        <is>
-          <t>Produktionsanlæg og maskiner</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="n"/>
-      <c r="C7" s="16" t="n"/>
-      <c r="D7" s="16" t="n"/>
-      <c r="E7" s="16" t="n"/>
-      <c r="F7" s="16" t="n">
-        <v>1072000</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="15" t="inlineStr">
-        <is>
-          <t>Driftsmateriel og inventar</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="n"/>
-      <c r="C8" s="16" t="n"/>
-      <c r="D8" s="16" t="n"/>
-      <c r="E8" s="16" t="n"/>
-      <c r="F8" s="16" t="n">
-        <v>36800</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="15" t="inlineStr">
-        <is>
-          <t>Indretning af lejede lokaler</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="n"/>
-      <c r="C9" s="16" t="n"/>
-      <c r="D9" s="16" t="n"/>
-      <c r="E9" s="16" t="n"/>
-      <c r="F9" s="16" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="15" t="inlineStr">
-        <is>
-          <t>Forudbetaling og anlægsaktiver under opførelse</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="n"/>
-      <c r="C10" s="16" t="n">
-        <v>354200</v>
-      </c>
-      <c r="D10" s="16" t="n">
-        <v>112700</v>
-      </c>
-      <c r="E10" s="16" t="n"/>
-      <c r="F10" s="16" t="n">
-        <v>174300</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="17" t="inlineStr">
-        <is>
-          <t>Materielle anlægsaktiver</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="n"/>
-      <c r="C11" s="16" t="n">
-        <v>21400</v>
-      </c>
-      <c r="D11" s="16" t="n">
-        <v>20700</v>
-      </c>
-      <c r="E11" s="16" t="n">
-        <v>1388400</v>
-      </c>
-      <c r="F11" s="16" t="n">
-        <v>1656000</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="15" t="inlineStr">
-        <is>
-          <t>Kapitalandele, dattervirksomheder</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="n"/>
-      <c r="C12" s="16" t="n"/>
-      <c r="D12" s="16" t="n"/>
-      <c r="E12" s="16" t="n"/>
-      <c r="F12" s="16" t="n">
+      <c r="D36" s="17" t="n"/>
+      <c r="E36" s="17" t="n">
+        <v>60700</v>
+      </c>
+      <c r="F36" s="17" t="n">
+        <v>72300</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="15" t="inlineStr">
+        <is>
+          <t>Hensatte forpligtelser</t>
+        </is>
+      </c>
+      <c r="B37" s="17" t="n">
+        <v>9600</v>
+      </c>
+      <c r="C37" s="17" t="n">
+        <v>20300</v>
+      </c>
+      <c r="D37" s="17" t="n">
+        <v>20100</v>
+      </c>
+      <c r="E37" s="17" t="n">
+        <v>60700</v>
+      </c>
+      <c r="F37" s="17" t="n">
+        <v>13700</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="16" t="inlineStr">
+        <is>
+          <t>Ansvarlig lånekapital (langfristet)</t>
+        </is>
+      </c>
+      <c r="B38" s="17" t="n"/>
+      <c r="C38" s="17" t="n"/>
+      <c r="D38" s="17" t="n"/>
+      <c r="E38" s="17" t="n"/>
+      <c r="F38" s="17" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="16" t="inlineStr">
+        <is>
+          <t>Langfristede lån</t>
+        </is>
+      </c>
+      <c r="B39" s="17" t="n"/>
+      <c r="C39" s="17" t="n"/>
+      <c r="D39" s="17" t="n"/>
+      <c r="E39" s="17" t="n">
+        <v>670300</v>
+      </c>
+      <c r="F39" s="17" t="n">
+        <v>525000</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="16" t="inlineStr">
+        <is>
+          <t>Leasingforpligtelser (langfristet)</t>
+        </is>
+      </c>
+      <c r="B40" s="17" t="n">
+        <v>62800</v>
+      </c>
+      <c r="C40" s="17" t="n">
+        <v>53400</v>
+      </c>
+      <c r="D40" s="17" t="n">
+        <v>44700</v>
+      </c>
+      <c r="E40" s="17" t="n"/>
+      <c r="F40" s="17" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="16" t="inlineStr">
+        <is>
+          <t>Anden gæld (langfristet)</t>
+        </is>
+      </c>
+      <c r="B41" s="17" t="n">
+        <v>782000</v>
+      </c>
+      <c r="C41" s="17" t="n">
+        <v>860300</v>
+      </c>
+      <c r="D41" s="17" t="n">
+        <v>800</v>
+      </c>
+      <c r="E41" s="17" t="n">
         <v>0</v>
       </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="15" t="inlineStr">
-        <is>
-          <t>Deposita</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="n">
-        <v>2600</v>
-      </c>
-      <c r="C13" s="16" t="n">
-        <v>2600</v>
-      </c>
-      <c r="D13" s="16" t="n">
-        <v>2900</v>
-      </c>
-      <c r="E13" s="16" t="n"/>
-      <c r="F13" s="16" t="n">
+      <c r="F41" s="17" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="17" t="inlineStr">
-        <is>
-          <t>Finansielle anlægsaktiver</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="n"/>
-      <c r="C14" s="16" t="n"/>
-      <c r="D14" s="16" t="n"/>
-      <c r="E14" s="16" t="n"/>
-      <c r="F14" s="16" t="n">
+    <row r="42">
+      <c r="A42" s="15" t="inlineStr">
+        <is>
+          <t>Langfristede gældsforpligtelser</t>
+        </is>
+      </c>
+      <c r="B42" s="17" t="n">
+        <v>897500</v>
+      </c>
+      <c r="C42" s="17" t="n">
+        <v>995200</v>
+      </c>
+      <c r="D42" s="17" t="n">
+        <v>881600</v>
+      </c>
+      <c r="E42" s="17" t="n">
+        <v>743100</v>
+      </c>
+      <c r="F42" s="17" t="n">
+        <v>621100</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="16" t="inlineStr">
+        <is>
+          <t>Ansvarlig lånekapital (kortfristet)</t>
+        </is>
+      </c>
+      <c r="B43" s="17" t="n"/>
+      <c r="C43" s="17" t="n"/>
+      <c r="D43" s="17" t="n"/>
+      <c r="E43" s="17" t="n"/>
+      <c r="F43" s="17" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="16" t="inlineStr">
+        <is>
+          <t>Kortfristet del af langfristede gældsforpligtelser</t>
+        </is>
+      </c>
+      <c r="B44" s="17" t="n"/>
+      <c r="C44" s="17" t="n"/>
+      <c r="D44" s="17" t="n"/>
+      <c r="E44" s="17" t="n"/>
+      <c r="F44" s="17" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="16" t="inlineStr">
+        <is>
+          <t>Kreditinstitutter</t>
+        </is>
+      </c>
+      <c r="B45" s="17" t="n">
+        <v>98100</v>
+      </c>
+      <c r="C45" s="17" t="n">
+        <v>105500</v>
+      </c>
+      <c r="D45" s="17" t="n"/>
+      <c r="E45" s="17" t="n">
+        <v>70200</v>
+      </c>
+      <c r="F45" s="17" t="n">
+        <v>68800</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="16" t="inlineStr">
+        <is>
+          <t>Leasingforpligtelser (kortfristet)</t>
+        </is>
+      </c>
+      <c r="B46" s="17" t="n">
+        <v>11900</v>
+      </c>
+      <c r="C46" s="17" t="n">
+        <v>13500</v>
+      </c>
+      <c r="D46" s="17" t="n">
+        <v>13200</v>
+      </c>
+      <c r="E46" s="17" t="n"/>
+      <c r="F46" s="17" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="16" t="inlineStr">
+        <is>
+          <t>Leverandører af varer og tjenesteydelser</t>
+        </is>
+      </c>
+      <c r="B47" s="17" t="n">
+        <v>306700</v>
+      </c>
+      <c r="C47" s="17" t="n">
+        <v>319700</v>
+      </c>
+      <c r="D47" s="17" t="n">
+        <v>301800</v>
+      </c>
+      <c r="E47" s="17" t="n">
+        <v>330200</v>
+      </c>
+      <c r="F47" s="17" t="n">
+        <v>322400</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="16" t="inlineStr">
+        <is>
+          <t>Gæld til tilknyttede virksomheder</t>
+        </is>
+      </c>
+      <c r="B48" s="17" t="n"/>
+      <c r="C48" s="17" t="n"/>
+      <c r="D48" s="17" t="n"/>
+      <c r="E48" s="17" t="n">
+        <v>24300</v>
+      </c>
+      <c r="F48" s="17" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="17" t="inlineStr">
-        <is>
-          <t>Anlægsaktiver</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="n">
-        <v>1423700</v>
-      </c>
-      <c r="C15" s="16" t="n">
-        <v>1812600</v>
-      </c>
-      <c r="D15" s="16" t="n">
-        <v>1630800</v>
-      </c>
-      <c r="E15" s="16" t="n">
-        <v>1577900</v>
-      </c>
-      <c r="F15" s="16" t="n">
-        <v>1744900</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="17" t="inlineStr">
-        <is>
-          <t>Varebeholdninger</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="n">
-        <v>256700</v>
-      </c>
-      <c r="C16" s="16" t="n">
-        <v>299900</v>
-      </c>
-      <c r="D16" s="16" t="n">
-        <v>327600</v>
-      </c>
-      <c r="E16" s="16" t="n">
-        <v>340400</v>
-      </c>
-      <c r="F16" s="16" t="n">
-        <v>389000</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="15" t="inlineStr">
-        <is>
-          <t>Tilgodehavender fra salg og tjenesteydelser</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="n">
-        <v>347800</v>
-      </c>
-      <c r="C17" s="16" t="n">
-        <v>396200</v>
-      </c>
-      <c r="D17" s="16" t="n">
-        <v>459500</v>
-      </c>
-      <c r="E17" s="16" t="n">
-        <v>457000</v>
-      </c>
-      <c r="F17" s="16" t="n">
-        <v>527100</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="15" t="inlineStr">
-        <is>
-          <t>Tilgodehavender hos tilknyttede virksomheder</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="n"/>
-      <c r="C18" s="16" t="n"/>
-      <c r="D18" s="16" t="n"/>
-      <c r="E18" s="16" t="n"/>
-      <c r="F18" s="16" t="n">
-        <v>102800</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="15" t="inlineStr">
-        <is>
-          <t>Andre tilgodehavender</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="n"/>
-      <c r="C19" s="16" t="n">
-        <v>14200</v>
-      </c>
-      <c r="D19" s="16" t="n">
-        <v>17500</v>
-      </c>
-      <c r="E19" s="16" t="n"/>
-      <c r="F19" s="16" t="n">
-        <v>94300</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="15" t="inlineStr">
-        <is>
-          <t>Periodeafgrænsningsposter (aktiver)</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="n">
-        <v>35100</v>
-      </c>
-      <c r="C20" s="16" t="n"/>
-      <c r="D20" s="16" t="n"/>
-      <c r="E20" s="16" t="n">
-        <v>37600</v>
-      </c>
-      <c r="F20" s="16" t="n">
-        <v>48100</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="15" t="inlineStr">
-        <is>
-          <t>Udskudt skatteaktiv</t>
-        </is>
-      </c>
-      <c r="B21" s="16" t="n">
-        <v>41200</v>
-      </c>
-      <c r="C21" s="16" t="n">
-        <v>62000</v>
-      </c>
-      <c r="D21" s="16" t="n">
-        <v>63200</v>
-      </c>
-      <c r="E21" s="16" t="n">
-        <v>54700</v>
-      </c>
-      <c r="F21" s="16" t="n">
-        <v>57200</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="15" t="inlineStr">
-        <is>
-          <t>Tilgodehavende skat hos tilknyttede virksomheder</t>
-        </is>
-      </c>
-      <c r="B22" s="16" t="n"/>
-      <c r="C22" s="16" t="n"/>
-      <c r="D22" s="16" t="n"/>
-      <c r="E22" s="16" t="n"/>
-      <c r="F22" s="16" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="15" t="inlineStr">
-        <is>
-          <t>Kortfristede skattetilgodehavender</t>
-        </is>
-      </c>
-      <c r="B23" s="16" t="n">
-        <v>15000</v>
-      </c>
-      <c r="C23" s="16" t="n">
-        <v>28100</v>
-      </c>
-      <c r="D23" s="16" t="n">
-        <v>24200</v>
-      </c>
-      <c r="E23" s="16" t="n">
-        <v>13400</v>
-      </c>
-      <c r="F23" s="16" t="n">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="17" t="inlineStr">
-        <is>
-          <t>Tilgodehavender</t>
-        </is>
-      </c>
-      <c r="B24" s="16" t="n">
-        <v>86400</v>
-      </c>
-      <c r="C24" s="16" t="n">
-        <v>125200</v>
-      </c>
-      <c r="D24" s="16" t="n">
-        <v>209200</v>
-      </c>
-      <c r="E24" s="16" t="n">
-        <v>108900</v>
-      </c>
-      <c r="F24" s="16" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="15" t="inlineStr">
-        <is>
-          <t>Værdipapirer</t>
-        </is>
-      </c>
-      <c r="B25" s="16" t="n"/>
-      <c r="C25" s="16" t="n"/>
-      <c r="D25" s="16" t="n"/>
-      <c r="E25" s="16" t="n"/>
-      <c r="F25" s="16" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="15" t="inlineStr">
-        <is>
-          <t>Likvide beholdninger</t>
-        </is>
-      </c>
-      <c r="B26" s="16" t="n">
-        <v>255100</v>
-      </c>
-      <c r="C26" s="16" t="n">
-        <v>144800</v>
-      </c>
-      <c r="D26" s="16" t="n">
-        <v>180200</v>
-      </c>
-      <c r="E26" s="16" t="n">
-        <v>298200</v>
-      </c>
-      <c r="F26" s="16" t="n">
-        <v>250300</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="17" t="inlineStr">
-        <is>
-          <t>Omsætningsaktiver</t>
-        </is>
-      </c>
-      <c r="B27" s="16" t="n">
-        <v>950500</v>
-      </c>
-      <c r="C27" s="16" t="n">
-        <v>991600</v>
-      </c>
-      <c r="D27" s="16" t="n">
-        <v>1226200</v>
-      </c>
-      <c r="E27" s="16" t="n">
-        <v>1143700</v>
-      </c>
-      <c r="F27" s="16" t="n">
-        <v>1412300</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="17" t="inlineStr">
-        <is>
-          <t>Aktiver</t>
-        </is>
-      </c>
-      <c r="B28" s="16" t="n">
-        <v>2374200</v>
-      </c>
-      <c r="C28" s="16" t="n">
+    <row r="49">
+      <c r="A49" s="16" t="inlineStr">
+        <is>
+          <t>Gæld til selskabsdeltagere og ledelse</t>
+        </is>
+      </c>
+      <c r="B49" s="17" t="n"/>
+      <c r="C49" s="17" t="n"/>
+      <c r="D49" s="17" t="n"/>
+      <c r="E49" s="17" t="n"/>
+      <c r="F49" s="17" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="16" t="inlineStr">
+        <is>
+          <t>Selskabsskat</t>
+        </is>
+      </c>
+      <c r="B50" s="17" t="n"/>
+      <c r="C50" s="17" t="n"/>
+      <c r="D50" s="17" t="n"/>
+      <c r="E50" s="17" t="n">
+        <v>43200</v>
+      </c>
+      <c r="F50" s="17" t="n">
+        <v>51000</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="16" t="inlineStr">
+        <is>
+          <t>Gæld til tilknyttede virksomheder vedr. selskabsskat</t>
+        </is>
+      </c>
+      <c r="B51" s="17" t="n"/>
+      <c r="C51" s="17" t="n"/>
+      <c r="D51" s="17" t="n"/>
+      <c r="E51" s="17" t="n"/>
+      <c r="F51" s="17" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="16" t="inlineStr">
+        <is>
+          <t>Anden gæld (kortfristet)</t>
+        </is>
+      </c>
+      <c r="B52" s="17" t="n">
+        <v>160700</v>
+      </c>
+      <c r="C52" s="17" t="n">
+        <v>150100</v>
+      </c>
+      <c r="D52" s="17" t="n">
+        <v>240900</v>
+      </c>
+      <c r="E52" s="17" t="n">
+        <v>264800</v>
+      </c>
+      <c r="F52" s="17" t="n">
+        <v>292600</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="16" t="inlineStr">
+        <is>
+          <t>Periodeafgrænsningsposter (passiver)</t>
+        </is>
+      </c>
+      <c r="B53" s="17" t="n"/>
+      <c r="C53" s="17" t="n"/>
+      <c r="D53" s="17" t="n"/>
+      <c r="E53" s="17" t="n">
+        <v>8300</v>
+      </c>
+      <c r="F53" s="17" t="n">
+        <v>56600</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="15" t="inlineStr">
+        <is>
+          <t>Kortfristede gældsforpligtelser</t>
+        </is>
+      </c>
+      <c r="B54" s="17" t="n">
+        <v>710200</v>
+      </c>
+      <c r="C54" s="17" t="n">
+        <v>713100</v>
+      </c>
+      <c r="D54" s="17" t="n">
+        <v>617300</v>
+      </c>
+      <c r="E54" s="17" t="n">
+        <v>741400</v>
+      </c>
+      <c r="F54" s="17" t="n">
+        <v>792500</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="15" t="inlineStr">
+        <is>
+          <t>Gældsforpligtelser</t>
+        </is>
+      </c>
+      <c r="B55" s="17" t="n">
+        <v>1607700</v>
+      </c>
+      <c r="C55" s="17" t="n">
+        <v>1708300</v>
+      </c>
+      <c r="D55" s="17" t="n">
+        <v>1498900</v>
+      </c>
+      <c r="E55" s="17" t="n">
+        <v>1484500</v>
+      </c>
+      <c r="F55" s="17" t="n">
+        <v>1413600</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="15" t="inlineStr">
+        <is>
+          <t>Passiver</t>
+        </is>
+      </c>
+      <c r="B56" s="17" t="n">
         <v>2804200</v>
       </c>
-      <c r="D28" s="16" t="n">
+      <c r="C56" s="17" t="n">
         <v>2948500</v>
       </c>
-      <c r="E28" s="16" t="n">
+      <c r="D56" s="17" t="n">
         <v>2723500</v>
       </c>
-      <c r="F28" s="16" t="n">
+      <c r="E56" s="17" t="n">
         <v>3157200</v>
       </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="15" t="inlineStr">
-        <is>
-          <t>Selskabskapital</t>
-        </is>
-      </c>
-      <c r="B29" s="16" t="n">
-        <v>140300</v>
-      </c>
-      <c r="C29" s="16" t="n">
-        <v>140300</v>
-      </c>
-      <c r="D29" s="16" t="n">
-        <v>140300</v>
-      </c>
-      <c r="E29" s="16" t="n">
-        <v>140300</v>
-      </c>
-      <c r="F29" s="16" t="n">
-        <v>140300</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="15" t="inlineStr">
-        <is>
-          <t>Reserve for nettoopskrivning (indre værdis metode)</t>
-        </is>
-      </c>
-      <c r="B30" s="16" t="n"/>
-      <c r="C30" s="16" t="n"/>
-      <c r="D30" s="16" t="n"/>
-      <c r="E30" s="16" t="n"/>
-      <c r="F30" s="16" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="15" t="inlineStr">
-        <is>
-          <t>Reserve for udviklingsomkostninger</t>
-        </is>
-      </c>
-      <c r="B31" s="16" t="n"/>
-      <c r="C31" s="16" t="n"/>
-      <c r="D31" s="16" t="n"/>
-      <c r="E31" s="16" t="n"/>
-      <c r="F31" s="16" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="15" t="inlineStr">
-        <is>
-          <t>Reserve for sikringstransaktioner</t>
-        </is>
-      </c>
-      <c r="B32" s="16" t="n"/>
-      <c r="C32" s="16" t="n"/>
-      <c r="D32" s="16" t="n"/>
-      <c r="E32" s="16" t="n"/>
-      <c r="F32" s="16" t="n">
-        <v>-4500</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="15" t="inlineStr">
-        <is>
-          <t>Andre reserver</t>
-        </is>
-      </c>
-      <c r="B33" s="16" t="n"/>
-      <c r="C33" s="16" t="n">
-        <v>-7800</v>
-      </c>
-      <c r="D33" s="16" t="n">
-        <v>-400</v>
-      </c>
-      <c r="E33" s="16" t="n">
-        <v>-12200</v>
-      </c>
-      <c r="F33" s="16" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="15" t="inlineStr">
-        <is>
-          <t>Overført resultat</t>
-        </is>
-      </c>
-      <c r="B34" s="16" t="n">
-        <v>1177100</v>
-      </c>
-      <c r="C34" s="16" t="n">
-        <v>1270000</v>
-      </c>
-      <c r="D34" s="16" t="n">
-        <v>1230900</v>
-      </c>
-      <c r="E34" s="16" t="n">
-        <v>1344800</v>
-      </c>
-      <c r="F34" s="16" t="n">
-        <v>1921900</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="17" t="inlineStr">
-        <is>
-          <t>Egenkapital i alt</t>
-        </is>
-      </c>
-      <c r="B35" s="16" t="n">
-        <v>1025300</v>
-      </c>
-      <c r="C35" s="16" t="n">
-        <v>1196500</v>
-      </c>
-      <c r="D35" s="16" t="n">
-        <v>1221800</v>
-      </c>
-      <c r="E35" s="16" t="n">
-        <v>1224600</v>
-      </c>
-      <c r="F35" s="16" t="n">
-        <v>1672700</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="15" t="inlineStr">
-        <is>
-          <t>Hensættelse til udskudt skat</t>
-        </is>
-      </c>
-      <c r="B36" s="16" t="n">
-        <v>32700</v>
-      </c>
-      <c r="C36" s="16" t="n">
-        <v>39700</v>
-      </c>
-      <c r="D36" s="16" t="n">
-        <v>60300</v>
-      </c>
-      <c r="E36" s="16" t="n"/>
-      <c r="F36" s="16" t="n">
-        <v>60700</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="17" t="inlineStr">
-        <is>
-          <t>Hensatte forpligtelser</t>
-        </is>
-      </c>
-      <c r="B37" s="16" t="n">
-        <v>35200</v>
-      </c>
-      <c r="C37" s="16" t="n">
-        <v>9600</v>
-      </c>
-      <c r="D37" s="16" t="n">
-        <v>20300</v>
-      </c>
-      <c r="E37" s="16" t="n">
-        <v>20100</v>
-      </c>
-      <c r="F37" s="16" t="n">
-        <v>60700</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="15" t="inlineStr">
-        <is>
-          <t>Ansvarlig lånekapital (langfristet)</t>
-        </is>
-      </c>
-      <c r="B38" s="16" t="n"/>
-      <c r="C38" s="16" t="n"/>
-      <c r="D38" s="16" t="n"/>
-      <c r="E38" s="16" t="n"/>
-      <c r="F38" s="16" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="15" t="inlineStr">
-        <is>
-          <t>Langfristede lån</t>
-        </is>
-      </c>
-      <c r="B39" s="16" t="n"/>
-      <c r="C39" s="16" t="n"/>
-      <c r="D39" s="16" t="n"/>
-      <c r="E39" s="16" t="n"/>
-      <c r="F39" s="16" t="n">
-        <v>670300</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="15" t="inlineStr">
-        <is>
-          <t>Leasingforpligtelser (langfristet)</t>
-        </is>
-      </c>
-      <c r="B40" s="16" t="n">
-        <v>59700</v>
-      </c>
-      <c r="C40" s="16" t="n">
-        <v>62800</v>
-      </c>
-      <c r="D40" s="16" t="n">
-        <v>53400</v>
-      </c>
-      <c r="E40" s="16" t="n">
-        <v>44700</v>
-      </c>
-      <c r="F40" s="16" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="15" t="inlineStr">
-        <is>
-          <t>Anden gæld (langfristet)</t>
-        </is>
-      </c>
-      <c r="B41" s="16" t="n">
-        <v>100</v>
-      </c>
-      <c r="C41" s="16" t="n">
-        <v>782000</v>
-      </c>
-      <c r="D41" s="16" t="n">
-        <v>860300</v>
-      </c>
-      <c r="E41" s="16" t="n">
-        <v>800</v>
-      </c>
-      <c r="F41" s="16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="17" t="inlineStr">
-        <is>
-          <t>Langfristede gældsforpligtelser</t>
-        </is>
-      </c>
-      <c r="B42" s="16" t="n">
-        <v>758600</v>
-      </c>
-      <c r="C42" s="16" t="n">
-        <v>897500</v>
-      </c>
-      <c r="D42" s="16" t="n">
-        <v>995200</v>
-      </c>
-      <c r="E42" s="16" t="n">
-        <v>881600</v>
-      </c>
-      <c r="F42" s="16" t="n">
-        <v>743100</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="15" t="inlineStr">
-        <is>
-          <t>Ansvarlig lånekapital (kortfristet)</t>
-        </is>
-      </c>
-      <c r="B43" s="16" t="n"/>
-      <c r="C43" s="16" t="n"/>
-      <c r="D43" s="16" t="n"/>
-      <c r="E43" s="16" t="n"/>
-      <c r="F43" s="16" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="15" t="inlineStr">
-        <is>
-          <t>Kortfristet del af langfristede gældsforpligtelser</t>
-        </is>
-      </c>
-      <c r="B44" s="16" t="n"/>
-      <c r="C44" s="16" t="n"/>
-      <c r="D44" s="16" t="n"/>
-      <c r="E44" s="16" t="n"/>
-      <c r="F44" s="16" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="15" t="inlineStr">
-        <is>
-          <t>Kreditinstitutter</t>
-        </is>
-      </c>
-      <c r="B45" s="16" t="n"/>
-      <c r="C45" s="16" t="n">
-        <v>98100</v>
-      </c>
-      <c r="D45" s="16" t="n">
-        <v>105500</v>
-      </c>
-      <c r="E45" s="16" t="n"/>
-      <c r="F45" s="16" t="n">
-        <v>70200</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="15" t="inlineStr">
-        <is>
-          <t>Leasingforpligtelser (kortfristet)</t>
-        </is>
-      </c>
-      <c r="B46" s="16" t="n">
-        <v>8900</v>
-      </c>
-      <c r="C46" s="16" t="n">
-        <v>11900</v>
-      </c>
-      <c r="D46" s="16" t="n">
-        <v>13500</v>
-      </c>
-      <c r="E46" s="16" t="n">
-        <v>13200</v>
-      </c>
-      <c r="F46" s="16" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="15" t="inlineStr">
-        <is>
-          <t>Leverandører af varer og tjenesteydelser</t>
-        </is>
-      </c>
-      <c r="B47" s="16" t="n">
-        <v>209600</v>
-      </c>
-      <c r="C47" s="16" t="n">
-        <v>306700</v>
-      </c>
-      <c r="D47" s="16" t="n">
-        <v>319700</v>
-      </c>
-      <c r="E47" s="16" t="n">
-        <v>301800</v>
-      </c>
-      <c r="F47" s="16" t="n">
-        <v>330200</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="15" t="inlineStr">
-        <is>
-          <t>Gæld til tilknyttede virksomheder</t>
-        </is>
-      </c>
-      <c r="B48" s="16" t="n"/>
-      <c r="C48" s="16" t="n"/>
-      <c r="D48" s="16" t="n"/>
-      <c r="E48" s="16" t="n"/>
-      <c r="F48" s="16" t="n">
-        <v>24300</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="15" t="inlineStr">
-        <is>
-          <t>Gæld til selskabsdeltagere og ledelse</t>
-        </is>
-      </c>
-      <c r="B49" s="16" t="n"/>
-      <c r="C49" s="16" t="n"/>
-      <c r="D49" s="16" t="n"/>
-      <c r="E49" s="16" t="n"/>
-      <c r="F49" s="16" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="15" t="inlineStr">
-        <is>
-          <t>Selskabsskat</t>
-        </is>
-      </c>
-      <c r="B50" s="16" t="n"/>
-      <c r="C50" s="16" t="n"/>
-      <c r="D50" s="16" t="n"/>
-      <c r="E50" s="16" t="n"/>
-      <c r="F50" s="16" t="n">
-        <v>43200</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="15" t="inlineStr">
-        <is>
-          <t>Gæld til tilknyttede virksomheder vedr. selskabsskat</t>
-        </is>
-      </c>
-      <c r="B51" s="16" t="n"/>
-      <c r="C51" s="16" t="n"/>
-      <c r="D51" s="16" t="n"/>
-      <c r="E51" s="16" t="n"/>
-      <c r="F51" s="16" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="15" t="inlineStr">
-        <is>
-          <t>Anden gæld (kortfristet)</t>
-        </is>
-      </c>
-      <c r="B52" s="16" t="n">
-        <v>171400</v>
-      </c>
-      <c r="C52" s="16" t="n">
-        <v>160700</v>
-      </c>
-      <c r="D52" s="16" t="n">
-        <v>150100</v>
-      </c>
-      <c r="E52" s="16" t="n">
-        <v>240900</v>
-      </c>
-      <c r="F52" s="16" t="n">
-        <v>264800</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="15" t="inlineStr">
-        <is>
-          <t>Periodeafgrænsningsposter (passiver)</t>
-        </is>
-      </c>
-      <c r="B53" s="16" t="n"/>
-      <c r="C53" s="16" t="n"/>
-      <c r="D53" s="16" t="n"/>
-      <c r="E53" s="16" t="n"/>
-      <c r="F53" s="16" t="n">
-        <v>8300</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="17" t="inlineStr">
-        <is>
-          <t>Kortfristede gældsforpligtelser</t>
-        </is>
-      </c>
-      <c r="B54" s="16" t="n">
-        <v>590300</v>
-      </c>
-      <c r="C54" s="16" t="n">
-        <v>710200</v>
-      </c>
-      <c r="D54" s="16" t="n">
-        <v>713100</v>
-      </c>
-      <c r="E54" s="16" t="n">
-        <v>617300</v>
-      </c>
-      <c r="F54" s="16" t="n">
-        <v>741400</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="17" t="inlineStr">
-        <is>
-          <t>Gældsforpligtelser</t>
-        </is>
-      </c>
-      <c r="B55" s="16" t="n">
-        <v>1348900</v>
-      </c>
-      <c r="C55" s="16" t="n">
-        <v>1607700</v>
-      </c>
-      <c r="D55" s="16" t="n">
-        <v>1708300</v>
-      </c>
-      <c r="E55" s="16" t="n">
-        <v>1498900</v>
-      </c>
-      <c r="F55" s="16" t="n">
-        <v>1484500</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="17" t="inlineStr">
-        <is>
-          <t>Passiver</t>
-        </is>
-      </c>
-      <c r="B56" s="16" t="n">
-        <v>2374200</v>
-      </c>
-      <c r="C56" s="16" t="n">
-        <v>2804200</v>
-      </c>
-      <c r="D56" s="16" t="n">
-        <v>2948500</v>
-      </c>
-      <c r="E56" s="16" t="n">
-        <v>2723500</v>
-      </c>
-      <c r="F56" s="16" t="n">
-        <v>3157200</v>
+      <c r="F56" s="17" t="n">
+        <v>3315800</v>
       </c>
     </row>
   </sheetData>
@@ -5969,6 +6140,128 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="72" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Pengestrømsopgørelse (t.kr.)</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C1" s="3" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D1" s="3" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E1" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F1" s="3" t="n">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra driftsaktivitet</t>
+        </is>
+      </c>
+      <c r="B2" s="17" t="n">
+        <v>240900</v>
+      </c>
+      <c r="C2" s="17" t="n">
+        <v>204400</v>
+      </c>
+      <c r="D2" s="17" t="n">
+        <v>622700</v>
+      </c>
+      <c r="E2" s="17" t="n">
+        <v>637200</v>
+      </c>
+      <c r="F2" s="17" t="n">
+        <v>720000</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra investeringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B3" s="17" t="n">
+        <v>-526600</v>
+      </c>
+      <c r="C3" s="17" t="n">
+        <v>-181700</v>
+      </c>
+      <c r="D3" s="17" t="n">
+        <v>-284200</v>
+      </c>
+      <c r="E3" s="17" t="n">
+        <v>-501400</v>
+      </c>
+      <c r="F3" s="17" t="n">
+        <v>-422200</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra finansieringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="n">
+        <v>233000</v>
+      </c>
+      <c r="C4" s="17" t="n">
+        <v>53800</v>
+      </c>
+      <c r="D4" s="17" t="n">
+        <v>-218200</v>
+      </c>
+      <c r="E4" s="17" t="n">
+        <v>-125400</v>
+      </c>
+      <c r="F4" s="17" t="n">
+        <v>-274900</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>Årets pengestrøm</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="n"/>
+      <c r="C5" s="17" t="n"/>
+      <c r="D5" s="17" t="n"/>
+      <c r="E5" s="17" t="n"/>
+      <c r="F5" s="17" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5999,13 +6292,13 @@
         </is>
       </c>
       <c r="B3" s="20" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C3" s="20" t="n">
         <v>2024</v>
       </c>
-      <c r="C3" s="20" t="n">
+      <c r="D3" s="20" t="n">
         <v>2023</v>
-      </c>
-      <c r="D3" s="20" t="n">
-        <v>2022</v>
       </c>
       <c r="F3" s="21" t="inlineStr">
         <is>
@@ -6695,7 +6988,7 @@
     <row r="39">
       <c r="A39" s="22" t="inlineStr">
         <is>
-          <t>Indekstal for indtjeningsevne (2022=100)</t>
+          <t>Indekstal for indtjeningsevne (2023=100)</t>
         </is>
       </c>
       <c r="B39" s="22" t="n"/>
@@ -6813,7 +7106,7 @@
     <row r="46">
       <c r="A46" s="22" t="inlineStr">
         <is>
-          <t>Indekstal for kapitaltilpasningsevne (2022=100)</t>
+          <t>Indekstal for kapitaltilpasningsevne (2023=100)</t>
         </is>
       </c>
       <c r="B46" s="22" t="n"/>
@@ -6989,7 +7282,7 @@
     <row r="57">
       <c r="A57" s="32" t="inlineStr">
         <is>
-          <t>Kilde: Bearbejdet uddrag af årsrapporter for 2022-2024. Alle dataceller er live formler der peger på res_raw / balance_raw.</t>
+          <t>Kilde: Bearbejdet uddrag af årsrapporter for 2023-2025. Alle dataceller er live formler der peger på res_raw / balance_raw.</t>
         </is>
       </c>
       <c r="B57" s="29" t="n"/>
@@ -7167,13 +7460,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -7212,27 +7505,27 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>2020 t.kr.</t>
+          <t>2021 t.kr.</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>2021 t.kr.</t>
+          <t>2022 t.kr.</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2022 t.kr.</t>
+          <t>2023 t.kr.</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>2023 t.kr.</t>
+          <t>2024 t.kr.</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>2024 t.kr.</t>
+          <t>2025 t.kr.</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
@@ -7260,10 +7553,10 @@
       <c r="D3" s="35" t="n"/>
       <c r="E3" s="35" t="n"/>
       <c r="F3" s="35" t="n"/>
-      <c r="G3" s="35" t="n"/>
-      <c r="H3" s="35" t="n">
+      <c r="G3" s="35" t="n">
         <v>0</v>
       </c>
+      <c r="H3" s="35" t="n"/>
       <c r="I3" s="36" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
@@ -7289,10 +7582,10 @@
       <c r="D4" s="38" t="n"/>
       <c r="E4" s="38" t="n"/>
       <c r="F4" s="38" t="n"/>
-      <c r="G4" s="38" t="n"/>
-      <c r="H4" s="38" t="n">
+      <c r="G4" s="38" t="n">
         <v>0</v>
       </c>
+      <c r="H4" s="38" t="n"/>
       <c r="I4" s="39" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
@@ -7318,9 +7611,11 @@
       <c r="D5" s="35" t="n"/>
       <c r="E5" s="35" t="n"/>
       <c r="F5" s="35" t="n"/>
-      <c r="G5" s="35" t="n"/>
+      <c r="G5" s="35" t="n">
+        <v>100000</v>
+      </c>
       <c r="H5" s="35" t="n">
-        <v>100000</v>
+        <v>-100000</v>
       </c>
       <c r="I5" s="36" t="inlineStr">
         <is>
@@ -7347,9 +7642,11 @@
       <c r="D6" s="38" t="n"/>
       <c r="E6" s="38" t="n"/>
       <c r="F6" s="38" t="n"/>
-      <c r="G6" s="38" t="n"/>
+      <c r="G6" s="38" t="n">
+        <v>400</v>
+      </c>
       <c r="H6" s="38" t="n">
-        <v>400</v>
+        <v>1100</v>
       </c>
       <c r="I6" s="39" t="inlineStr">
         <is>
@@ -7376,9 +7673,11 @@
       <c r="D7" s="35" t="n"/>
       <c r="E7" s="35" t="n"/>
       <c r="F7" s="35" t="n"/>
-      <c r="G7" s="35" t="n"/>
+      <c r="G7" s="35" t="n">
+        <v>10200</v>
+      </c>
       <c r="H7" s="35" t="n">
-        <v>10200</v>
+        <v>8400</v>
       </c>
       <c r="I7" s="36" t="inlineStr">
         <is>
@@ -7405,9 +7704,11 @@
       <c r="D8" s="38" t="n"/>
       <c r="E8" s="38" t="n"/>
       <c r="F8" s="38" t="n"/>
-      <c r="G8" s="38" t="n"/>
+      <c r="G8" s="38" t="n">
+        <v>-491500</v>
+      </c>
       <c r="H8" s="38" t="n">
-        <v>-491500</v>
+        <v>-588200</v>
       </c>
       <c r="I8" s="39" t="inlineStr">
         <is>
@@ -7434,7 +7735,9 @@
       <c r="D9" s="35" t="n"/>
       <c r="E9" s="35" t="n"/>
       <c r="F9" s="35" t="n"/>
-      <c r="G9" s="35" t="n"/>
+      <c r="G9" s="35" t="n">
+        <v>0</v>
+      </c>
       <c r="H9" s="35" t="n">
         <v>0</v>
       </c>
@@ -7452,21 +7755,21 @@
       </c>
       <c r="B10" s="37" t="inlineStr">
         <is>
-          <t>ifrs-full:AdjustmentsForReconcileProfitLoss</t>
+          <t>fsa:ShorttermReceivablesFromOwnersOtherCompanies</t>
         </is>
       </c>
       <c r="C10" s="37" t="inlineStr">
         <is>
-          <t>ifrs-full:AdjustmentsForReconcileProfitLoss</t>
-        </is>
-      </c>
-      <c r="D10" s="38" t="n">
-        <v>8200</v>
-      </c>
+          <t>fsa:ShorttermReceivablesFromOwnersOtherCompanies</t>
+        </is>
+      </c>
+      <c r="D10" s="38" t="n"/>
       <c r="E10" s="38" t="n"/>
       <c r="F10" s="38" t="n"/>
       <c r="G10" s="38" t="n"/>
-      <c r="H10" s="38" t="n"/>
+      <c r="H10" s="38" t="n">
+        <v>0</v>
+      </c>
       <c r="I10" s="39" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
@@ -7481,23 +7784,17 @@
       </c>
       <c r="B11" s="34" t="inlineStr">
         <is>
-          <t>ifrs-full:CurrentGovernmentGrants</t>
+          <t>ifrs-full:AdjustmentsForReconcileProfitLoss</t>
         </is>
       </c>
       <c r="C11" s="34" t="inlineStr">
         <is>
-          <t>ifrs-full:CurrentGovernmentGrants</t>
-        </is>
-      </c>
-      <c r="D11" s="35" t="n">
-        <v>900</v>
-      </c>
-      <c r="E11" s="35" t="n">
-        <v>900</v>
-      </c>
-      <c r="F11" s="35" t="n">
-        <v>100</v>
-      </c>
+          <t>ifrs-full:AdjustmentsForReconcileProfitLoss</t>
+        </is>
+      </c>
+      <c r="D11" s="35" t="n"/>
+      <c r="E11" s="35" t="n"/>
+      <c r="F11" s="35" t="n"/>
       <c r="G11" s="35" t="n"/>
       <c r="H11" s="35" t="n"/>
       <c r="I11" s="36" t="inlineStr">
@@ -7514,20 +7811,22 @@
       </c>
       <c r="B12" s="37" t="inlineStr">
         <is>
-          <t>ifrs-full:GainsLossesOnHedgesOfNetInvestmentsInForeignOperationsBeforeTax</t>
+          <t>ifrs-full:CurrentGovernmentGrants</t>
         </is>
       </c>
       <c r="C12" s="37" t="inlineStr">
         <is>
-          <t>ifrs-full:GainsLossesOnHedgesOfNetInvestmentsInForeignOperationsBeforeTax</t>
-        </is>
-      </c>
-      <c r="D12" s="38" t="n"/>
-      <c r="E12" s="38" t="n"/>
+          <t>ifrs-full:CurrentGovernmentGrants</t>
+        </is>
+      </c>
+      <c r="D12" s="38" t="n">
+        <v>900</v>
+      </c>
+      <c r="E12" s="38" t="n">
+        <v>100</v>
+      </c>
       <c r="F12" s="38" t="n"/>
-      <c r="G12" s="38" t="n">
-        <v>-151000</v>
-      </c>
+      <c r="G12" s="38" t="n"/>
       <c r="H12" s="38" t="n"/>
       <c r="I12" s="39" t="inlineStr">
         <is>
@@ -7543,20 +7842,18 @@
       </c>
       <c r="B13" s="34" t="inlineStr">
         <is>
-          <t>ifrs-full:GovernmentGrants</t>
+          <t>ifrs-full:GainsLossesOnHedgesOfNetInvestmentsInForeignOperationsBeforeTax</t>
         </is>
       </c>
       <c r="C13" s="34" t="inlineStr">
         <is>
-          <t>ifrs-full:GovernmentGrants</t>
+          <t>ifrs-full:GainsLossesOnHedgesOfNetInvestmentsInForeignOperationsBeforeTax</t>
         </is>
       </c>
       <c r="D13" s="35" t="n"/>
-      <c r="E13" s="35" t="n">
-        <v>500</v>
-      </c>
+      <c r="E13" s="35" t="n"/>
       <c r="F13" s="35" t="n">
-        <v>300</v>
+        <v>-151000</v>
       </c>
       <c r="G13" s="35" t="n"/>
       <c r="H13" s="35" t="n"/>
@@ -7574,21 +7871,21 @@
       </c>
       <c r="B14" s="37" t="inlineStr">
         <is>
-          <t>ifrs-full:IncomeTaxRelatingToChangeInValueOfForeignCurrencyBasisSpreadsOfOtherComprehensiveIncome</t>
+          <t>ifrs-full:GovernmentGrants</t>
         </is>
       </c>
       <c r="C14" s="37" t="inlineStr">
         <is>
-          <t>ifrs-full:IncomeTaxRelatingToChangeInValueOfForeignCurrencyBasisSpreadsOfOtherComprehensiveIncome</t>
-        </is>
-      </c>
-      <c r="D14" s="38" t="n"/>
+          <t>ifrs-full:GovernmentGrants</t>
+        </is>
+      </c>
+      <c r="D14" s="38" t="n">
+        <v>500</v>
+      </c>
       <c r="E14" s="38" t="n">
-        <v>-2900</v>
-      </c>
-      <c r="F14" s="38" t="n">
-        <v>800</v>
-      </c>
+        <v>300</v>
+      </c>
+      <c r="F14" s="38" t="n"/>
       <c r="G14" s="38" t="n"/>
       <c r="H14" s="38" t="n"/>
       <c r="I14" s="39" t="inlineStr">
@@ -7605,21 +7902,21 @@
       </c>
       <c r="B15" s="34" t="inlineStr">
         <is>
-          <t>ifrs-full:IncomeTaxRelatingToHedgesOfNetInvestmentsInForeignOperationsOfOtherComprehensiveIncome</t>
+          <t>ifrs-full:IncomeTaxRelatingToChangeInValueOfForeignCurrencyBasisSpreadsOfOtherComprehensiveIncome</t>
         </is>
       </c>
       <c r="C15" s="34" t="inlineStr">
         <is>
-          <t>ifrs-full:IncomeTaxRelatingToHedgesOfNetInvestmentsInForeignOperationsOfOtherComprehensiveIncome</t>
-        </is>
-      </c>
-      <c r="D15" s="35" t="n"/>
+          <t>ifrs-full:IncomeTaxRelatingToChangeInValueOfForeignCurrencyBasisSpreadsOfOtherComprehensiveIncome</t>
+        </is>
+      </c>
+      <c r="D15" s="35" t="n">
+        <v>-2900</v>
+      </c>
       <c r="E15" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" s="35" t="n">
         <v>800</v>
       </c>
+      <c r="F15" s="35" t="n"/>
       <c r="G15" s="35" t="n"/>
       <c r="H15" s="35" t="n"/>
       <c r="I15" s="36" t="inlineStr">
@@ -7636,21 +7933,21 @@
       </c>
       <c r="B16" s="37" t="inlineStr">
         <is>
-          <t>ifrs-full:Machinery</t>
+          <t>ifrs-full:IncomeTaxRelatingToHedgesOfNetInvestmentsInForeignOperationsOfOtherComprehensiveIncome</t>
         </is>
       </c>
       <c r="C16" s="37" t="inlineStr">
         <is>
-          <t>ifrs-full:Machinery</t>
-        </is>
-      </c>
-      <c r="D16" s="38" t="n"/>
+          <t>ifrs-full:IncomeTaxRelatingToHedgesOfNetInvestmentsInForeignOperationsOfOtherComprehensiveIncome</t>
+        </is>
+      </c>
+      <c r="D16" s="38" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="38" t="n">
-        <v>717800</v>
-      </c>
-      <c r="F16" s="38" t="n">
-        <v>876400</v>
-      </c>
+        <v>800</v>
+      </c>
+      <c r="F16" s="38" t="n"/>
       <c r="G16" s="38" t="n"/>
       <c r="H16" s="38" t="n"/>
       <c r="I16" s="39" t="inlineStr">
@@ -7667,19 +7964,21 @@
       </c>
       <c r="B17" s="34" t="inlineStr">
         <is>
-          <t>ifrs-full:NoncurrentAssetsOrDisposalGroupsClassifiedAsHeldForSaleOrAsHeldForDistributionToOwners</t>
+          <t>ifrs-full:Machinery</t>
         </is>
       </c>
       <c r="C17" s="34" t="inlineStr">
         <is>
-          <t>ifrs-full:NoncurrentAssetsOrDisposalGroupsClassifiedAsHeldForSaleOrAsHeldForDistributionToOwners</t>
-        </is>
-      </c>
-      <c r="D17" s="35" t="n"/>
-      <c r="E17" s="35" t="n"/>
-      <c r="F17" s="35" t="n">
-        <v>91500</v>
-      </c>
+          <t>ifrs-full:Machinery</t>
+        </is>
+      </c>
+      <c r="D17" s="35" t="n">
+        <v>717800</v>
+      </c>
+      <c r="E17" s="35" t="n">
+        <v>876400</v>
+      </c>
+      <c r="F17" s="35" t="n"/>
       <c r="G17" s="35" t="n"/>
       <c r="H17" s="35" t="n"/>
       <c r="I17" s="36" t="inlineStr">
@@ -7696,18 +7995,18 @@
       </c>
       <c r="B18" s="37" t="inlineStr">
         <is>
-          <t>ifrs-full:NoncurrentGovernmentGrants</t>
+          <t>ifrs-full:NoncurrentAssetsOrDisposalGroupsClassifiedAsHeldForSaleOrAsHeldForDistributionToOwners</t>
         </is>
       </c>
       <c r="C18" s="37" t="inlineStr">
         <is>
-          <t>ifrs-full:NoncurrentGovernmentGrants</t>
-        </is>
-      </c>
-      <c r="D18" s="38" t="n">
-        <v>1500</v>
-      </c>
-      <c r="E18" s="38" t="n"/>
+          <t>ifrs-full:NoncurrentAssetsOrDisposalGroupsClassifiedAsHeldForSaleOrAsHeldForDistributionToOwners</t>
+        </is>
+      </c>
+      <c r="D18" s="38" t="n"/>
+      <c r="E18" s="38" t="n">
+        <v>91500</v>
+      </c>
       <c r="F18" s="38" t="n"/>
       <c r="G18" s="38" t="n"/>
       <c r="H18" s="38" t="n"/>
@@ -7725,21 +8024,17 @@
       </c>
       <c r="B19" s="34" t="inlineStr">
         <is>
-          <t>ifrs-full:NoncurrentReceivablesDueFromRelatedParties</t>
+          <t>ifrs-full:NoncurrentGovernmentGrants</t>
         </is>
       </c>
       <c r="C19" s="34" t="inlineStr">
         <is>
-          <t>ifrs-full:NoncurrentReceivablesDueFromRelatedParties</t>
+          <t>ifrs-full:NoncurrentGovernmentGrants</t>
         </is>
       </c>
       <c r="D19" s="35" t="n"/>
-      <c r="E19" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="35" t="n">
-        <v>0</v>
-      </c>
+      <c r="E19" s="35" t="n"/>
+      <c r="F19" s="35" t="n"/>
       <c r="G19" s="35" t="n"/>
       <c r="H19" s="35" t="n"/>
       <c r="I19" s="36" t="inlineStr">
@@ -7756,21 +8051,21 @@
       </c>
       <c r="B20" s="37" t="inlineStr">
         <is>
-          <t>ifrs-full:Prepayments</t>
+          <t>ifrs-full:NoncurrentReceivablesDueFromRelatedParties</t>
         </is>
       </c>
       <c r="C20" s="37" t="inlineStr">
         <is>
-          <t>ifrs-full:Prepayments</t>
-        </is>
-      </c>
-      <c r="D20" s="38" t="n"/>
+          <t>ifrs-full:NoncurrentReceivablesDueFromRelatedParties</t>
+        </is>
+      </c>
+      <c r="D20" s="38" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="38" t="n">
-        <v>24300</v>
-      </c>
-      <c r="F20" s="38" t="n">
-        <v>25500</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F20" s="38" t="n"/>
       <c r="G20" s="38" t="n"/>
       <c r="H20" s="38" t="n"/>
       <c r="I20" s="39" t="inlineStr">
@@ -7787,24 +8082,55 @@
       </c>
       <c r="B21" s="34" t="inlineStr">
         <is>
-          <t>ifrs-full:ReserveOfExchangeDifferencesOnTranslation</t>
+          <t>ifrs-full:Prepayments</t>
         </is>
       </c>
       <c r="C21" s="34" t="inlineStr">
         <is>
-          <t>ifrs-full:ReserveOfExchangeDifferencesOnTranslation</t>
-        </is>
-      </c>
-      <c r="D21" s="35" t="n"/>
+          <t>ifrs-full:Prepayments</t>
+        </is>
+      </c>
+      <c r="D21" s="35" t="n">
+        <v>24300</v>
+      </c>
       <c r="E21" s="35" t="n">
-        <v>-206000</v>
-      </c>
-      <c r="F21" s="35" t="n">
-        <v>-149000</v>
-      </c>
+        <v>25500</v>
+      </c>
+      <c r="F21" s="35" t="n"/>
       <c r="G21" s="35" t="n"/>
       <c r="H21" s="35" t="n"/>
       <c r="I21" s="36" t="inlineStr">
+        <is>
+          <t>Ingen forklaring tilgængelig.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="37" t="inlineStr">
+        <is>
+          <t>Øvrige (ukendt)</t>
+        </is>
+      </c>
+      <c r="B22" s="37" t="inlineStr">
+        <is>
+          <t>ifrs-full:ReserveOfExchangeDifferencesOnTranslation</t>
+        </is>
+      </c>
+      <c r="C22" s="37" t="inlineStr">
+        <is>
+          <t>ifrs-full:ReserveOfExchangeDifferencesOnTranslation</t>
+        </is>
+      </c>
+      <c r="D22" s="38" t="n">
+        <v>-206000</v>
+      </c>
+      <c r="E22" s="38" t="n">
+        <v>-149000</v>
+      </c>
+      <c r="F22" s="38" t="n"/>
+      <c r="G22" s="38" t="n"/>
+      <c r="H22" s="38" t="n"/>
+      <c r="I22" s="39" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
         </is>
